--- a/Required weights.xlsx
+++ b/Required weights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofwaterloo-my.sharepoint.com/personal/maraji_uwaterloo_ca/Documents/Symbiosis Lab/Waqas/Side Projects/Bipartitie_3_way/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="276" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{514EE0A5-E9F4-9142-8B2F-3B10EBC16CC2}"/>
+  <xr:revisionPtr revIDLastSave="329" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4451FB81-DC32-204D-8F78-388D80952252}"/>
   <bookViews>
-    <workbookView xWindow="4160" yWindow="24920" windowWidth="17620" windowHeight="14820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8160" yWindow="2220" windowWidth="30240" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relationship Matrix" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="55">
   <si>
     <t>Communication</t>
   </si>
@@ -197,6 +197,12 @@
   </si>
   <si>
     <t>Parti</t>
+  </si>
+  <si>
+    <t>individual%</t>
+  </si>
+  <si>
+    <t>individual %</t>
   </si>
 </sst>
 </file>
@@ -394,7 +400,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -429,19 +435,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -451,6 +444,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -460,6 +464,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -602,6 +615,17 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -702,13 +726,24 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -716,12 +751,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -730,22 +764,43 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -754,172 +809,175 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -966,42 +1024,57 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1410,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C516A866-194E-4597-9029-A5AD387CCDD1}">
-  <dimension ref="B3:Y21"/>
+  <dimension ref="B3:AA21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -1418,960 +1491,1005 @@
     <col min="3" max="3" width="24.33203125" style="1" customWidth="1"/>
     <col min="4" max="18" width="4.1640625" style="1" customWidth="1"/>
     <col min="19" max="19" width="18.6640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="4.1640625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="1.1640625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="18" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.83203125" style="1"/>
+    <col min="23" max="24" width="8.83203125" style="1"/>
+    <col min="25" max="25" width="4.1640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="1.1640625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="18" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="10"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12" t="s">
+    <row r="3" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="12" t="s">
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="12" t="s">
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="13"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="12" t="s">
+      <c r="M4" s="20"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="14"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="21"/>
     </row>
-    <row r="5" spans="2:25" ht="139.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="17" t="s">
+    <row r="5" spans="2:27" ht="139.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="22"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="17" t="s">
+      <c r="L5" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="18" t="s">
+      <c r="M5" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="N5" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="17" t="s">
+      <c r="O5" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="P5" s="18" t="s">
+      <c r="P5" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="Q5" s="18" t="s">
+      <c r="Q5" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="R5" s="19" t="s">
+      <c r="R5" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="S5" s="98" t="s">
+      <c r="S5" s="101" t="s">
         <v>51</v>
       </c>
+      <c r="T5" s="115" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="6" spans="2:25" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="20" t="s">
+    <row r="6" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="P6" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="R6" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="S6" s="97">
+      <c r="D6" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="R6" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="S6" s="100">
         <v>10</v>
       </c>
+      <c r="T6">
+        <v>20</v>
+      </c>
     </row>
-    <row r="7" spans="2:25" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="29"/>
-      <c r="C7" s="30" t="s">
+    <row r="7" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="36"/>
+      <c r="C7" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q7" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="R7" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="S7" s="97"/>
+      <c r="D7" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="R7" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="S7" s="100"/>
+      <c r="T7">
+        <v>30</v>
+      </c>
     </row>
-    <row r="8" spans="2:25" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="43" t="s">
+    <row r="8" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="49"/>
+      <c r="C8" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q8" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="R8" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="S8" s="97"/>
-      <c r="T8" s="79"/>
-      <c r="U8" s="80"/>
-      <c r="V8" s="81"/>
+      <c r="D8" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="S8" s="100"/>
+      <c r="T8">
+        <v>50</v>
+      </c>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
-      <c r="Y8" s="3"/>
+      <c r="Y8" s="86"/>
+      <c r="Z8" s="87"/>
+      <c r="AA8" s="88"/>
     </row>
-    <row r="9" spans="2:25" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="20" t="s">
+    <row r="9" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="L9" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="N9" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="P9" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q9" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="R9" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="S9" s="97">
+      <c r="D9" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="R9" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="S9" s="100">
         <v>50</v>
       </c>
-      <c r="T9" s="82"/>
-      <c r="U9" s="80"/>
-      <c r="V9" s="83"/>
+      <c r="T9">
+        <v>20</v>
+      </c>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
-      <c r="Y9" s="3"/>
+      <c r="Y9" s="89"/>
+      <c r="Z9" s="87"/>
+      <c r="AA9" s="90"/>
     </row>
-    <row r="10" spans="2:25" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="29"/>
-      <c r="C10" s="30" t="s">
+    <row r="10" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="36"/>
+      <c r="C10" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="O10" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="P10" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q10" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="R10" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="S10" s="97"/>
-      <c r="T10" s="84"/>
-      <c r="U10" s="80"/>
-      <c r="V10" s="85"/>
+      <c r="D10" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="S10" s="100"/>
+      <c r="T10">
+        <v>35</v>
+      </c>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
-      <c r="Y10" s="3"/>
+      <c r="Y10" s="91"/>
+      <c r="Z10" s="87"/>
+      <c r="AA10" s="92"/>
     </row>
-    <row r="11" spans="2:25" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="29"/>
-      <c r="C11" s="30" t="s">
+    <row r="11" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="36"/>
+      <c r="C11" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="M11" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="P11" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q11" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="R11" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="S11" s="97"/>
-      <c r="T11" s="86"/>
-      <c r="U11" s="80"/>
-      <c r="V11" s="87"/>
+      <c r="D11" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="O11" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="R11" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="S11" s="100"/>
+      <c r="T11">
+        <v>40</v>
+      </c>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
-      <c r="Y11" s="3"/>
+      <c r="Y11" s="93"/>
+      <c r="Z11" s="87"/>
+      <c r="AA11" s="94"/>
     </row>
-    <row r="12" spans="2:25" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
-      <c r="C12" s="43" t="s">
+    <row r="12" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="49"/>
+      <c r="C12" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L12" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="M12" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="N12" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="P12" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q12" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="R12" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="S12" s="97"/>
+      <c r="D12" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="N12" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q12" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="R12" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="S12" s="100"/>
+      <c r="T12">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="2:25" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="20" t="s">
+    <row r="13" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="K13" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="N13" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="P13" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q13" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="R13" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="S13" s="97">
+      <c r="D13" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="62" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="62" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="S13" s="100">
         <v>25</v>
       </c>
-      <c r="T13" s="88" t="s">
-        <v>28</v>
-      </c>
-      <c r="U13" s="73"/>
-      <c r="V13" s="74" t="s">
+      <c r="T13">
+        <v>20</v>
+      </c>
+      <c r="Y13" s="95" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z13" s="80"/>
+      <c r="AA13" s="81" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="2:25" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="29"/>
-      <c r="C14" s="30" t="s">
+    <row r="14" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="36"/>
+      <c r="C14" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="L14" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="P14" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q14" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="R14" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="S14" s="97"/>
-      <c r="T14" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="U14" s="73"/>
-      <c r="V14" s="76" t="s">
+      <c r="D14" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="L14" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q14" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="R14" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="S14" s="100"/>
+      <c r="T14">
+        <v>40</v>
+      </c>
+      <c r="Y14" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z14" s="80"/>
+      <c r="AA14" s="83" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="2:25" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="29"/>
-      <c r="C15" s="30" t="s">
+    <row r="15" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="36"/>
+      <c r="C15" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="P15" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q15" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="R15" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="S15" s="97"/>
-      <c r="T15" s="77" t="s">
+      <c r="D15" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="O15" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q15" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="S15" s="100"/>
+      <c r="T15">
+        <v>25</v>
+      </c>
+      <c r="Y15" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="U15" s="73"/>
-      <c r="V15" s="78" t="s">
+      <c r="Z15" s="80"/>
+      <c r="AA15" s="85" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="2:25" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="56"/>
-      <c r="C16" s="57" t="s">
+    <row r="16" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="63"/>
+      <c r="C16" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="K16" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="L16" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="M16" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" s="64" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" s="65" t="s">
-        <v>26</v>
-      </c>
-      <c r="P16" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q16" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="R16" s="64" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="97"/>
+      <c r="D16" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="O16" s="72" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="R16" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="S16" s="100"/>
+      <c r="T16">
+        <v>15</v>
+      </c>
     </row>
-    <row r="17" spans="2:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="20" t="s">
+    <row r="17" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="M17" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="N17" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="O17" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="P17" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q17" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="R17" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="S17" s="97">
+      <c r="D17" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="M17" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="N17" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="O17" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="P17" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="R17" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="S17" s="100">
         <v>15</v>
       </c>
+      <c r="T17">
+        <v>30</v>
+      </c>
     </row>
-    <row r="18" spans="2:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="66"/>
-      <c r="C18" s="30" t="s">
+    <row r="18" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="73"/>
+      <c r="C18" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="M18" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N18" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="P18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q18" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="R18" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="S18" s="97"/>
+      <c r="D18" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="O18" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="R18" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="S18" s="100"/>
+      <c r="T18">
+        <v>45</v>
+      </c>
     </row>
-    <row r="19" spans="2:19" ht="38.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="66"/>
-      <c r="C19" s="67" t="s">
+    <row r="19" spans="2:20" ht="17" x14ac:dyDescent="0.2">
+      <c r="B19" s="73"/>
+      <c r="C19" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="M19" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="N19" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="O19" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="P19" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q19" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="R19" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="S19" s="97"/>
+      <c r="D19" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="N19" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="O19" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="R19" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="S19" s="100"/>
+      <c r="T19">
+        <v>15</v>
+      </c>
     </row>
-    <row r="20" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="68"/>
-      <c r="C20" s="69" t="s">
+    <row r="20" spans="2:20" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="75"/>
+      <c r="C20" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="K20" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="L20" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="M20" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="N20" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="P20" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q20" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="R20" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="S20" s="97"/>
+      <c r="D20" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="L20" s="78" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q20" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="R20" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="S20" s="100"/>
+      <c r="T20">
+        <v>10</v>
+      </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="C21" s="101" t="s">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C21" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="96">
+      <c r="D21" s="99">
         <v>40</v>
       </c>
-      <c r="E21" s="96"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="96">
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="99">
         <v>30</v>
       </c>
-      <c r="I21" s="96"/>
-      <c r="J21" s="96"/>
-      <c r="K21" s="96"/>
-      <c r="L21" s="96">
+      <c r="I21" s="99"/>
+      <c r="J21" s="99"/>
+      <c r="K21" s="99"/>
+      <c r="L21" s="99">
         <v>20</v>
       </c>
-      <c r="M21" s="96"/>
-      <c r="N21" s="96"/>
-      <c r="O21" s="96">
+      <c r="M21" s="99"/>
+      <c r="N21" s="99"/>
+      <c r="O21" s="99">
         <v>10</v>
       </c>
-      <c r="P21" s="96"/>
-      <c r="Q21" s="96"/>
-      <c r="R21" s="96"/>
+      <c r="P21" s="99"/>
+      <c r="Q21" s="99"/>
+      <c r="R21" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -2414,7 +2532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC40F516-73D9-AF40-BBFA-DA5A09FC7B78}">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.1640625" bestFit="1" customWidth="1"/>
@@ -2422,7 +2540,7 @@
     <col min="3" max="17" width="3.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1">
@@ -2473,137 +2591,137 @@
     </row>
     <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="90" t="s">
+      <c r="B2" s="104"/>
+      <c r="C2" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90" t="s">
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90" t="s">
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90" t="s">
+      <c r="L2" s="20"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="O2" s="90"/>
-      <c r="P2" s="90"/>
-      <c r="Q2" s="90"/>
-      <c r="R2" s="100" t="s">
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="102" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="127" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="91" t="s">
+      <c r="B3" s="104"/>
+      <c r="C3" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="91" t="s">
+      <c r="D3" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="91" t="s">
+      <c r="E3" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="91" t="s">
+      <c r="F3" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="91" t="s">
+      <c r="G3" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="91" t="s">
+      <c r="H3" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="91" t="s">
+      <c r="I3" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="91" t="s">
+      <c r="J3" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="91" t="s">
+      <c r="K3" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="91" t="s">
+      <c r="L3" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="91" t="s">
+      <c r="M3" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="91" t="s">
+      <c r="N3" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="91" t="s">
+      <c r="O3" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="91" t="s">
+      <c r="P3" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="91" t="s">
+      <c r="Q3" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="R3" s="95"/>
+      <c r="R3" s="98"/>
     </row>
     <row r="4" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>0</v>
       </c>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="R4" s="95">
+      <c r="C4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="113" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" s="98">
         <v>40</v>
       </c>
     </row>
@@ -2611,55 +2729,55 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="94" t="s">
+      <c r="B5" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="93" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="93" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="R5" s="95">
+      <c r="C5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="113" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="97" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" s="98">
         <v>25</v>
       </c>
     </row>
@@ -2667,55 +2785,55 @@
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="94" t="s">
+      <c r="B6" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="R6" s="95">
+      <c r="C6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="113" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="98">
         <v>15</v>
       </c>
     </row>
@@ -2723,55 +2841,55 @@
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="R7" s="95">
+      <c r="C7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="R7" s="98">
         <v>10</v>
       </c>
     </row>
@@ -2779,85 +2897,135 @@
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="R8" s="95">
+      <c r="C8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="R8" s="98">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="B9" s="99" t="s">
+      <c r="B9" s="105" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="96">
+      <c r="C9" s="108">
         <v>20</v>
       </c>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96">
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="109"/>
+      <c r="G9" s="108">
         <v>40</v>
       </c>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96">
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="109"/>
+      <c r="K9" s="108">
         <v>25</v>
       </c>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96">
+      <c r="L9" s="99"/>
+      <c r="M9" s="109"/>
+      <c r="N9" s="108">
         <v>15</v>
       </c>
-      <c r="O9" s="96"/>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="96"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="109"/>
+    </row>
+    <row r="10" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="114" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="110">
+        <v>20</v>
+      </c>
+      <c r="D10" s="111">
+        <v>30</v>
+      </c>
+      <c r="E10" s="111">
+        <v>15</v>
+      </c>
+      <c r="F10" s="112">
+        <v>35</v>
+      </c>
+      <c r="G10" s="110">
+        <v>25</v>
+      </c>
+      <c r="H10" s="111">
+        <v>30</v>
+      </c>
+      <c r="I10" s="111">
+        <v>30</v>
+      </c>
+      <c r="J10" s="112">
+        <v>15</v>
+      </c>
+      <c r="K10" s="110">
+        <v>50</v>
+      </c>
+      <c r="L10" s="111">
+        <v>30</v>
+      </c>
+      <c r="M10" s="112">
+        <v>20</v>
+      </c>
+      <c r="N10" s="110">
+        <v>35</v>
+      </c>
+      <c r="O10" s="111">
+        <v>25</v>
+      </c>
+      <c r="P10" s="111">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="112">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2895,58 +3063,58 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:18" ht="129" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="5" t="s">
         <v>21</v>
       </c>
     </row>

--- a/Required weights.xlsx
+++ b/Required weights.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofwaterloo-my.sharepoint.com/personal/maraji_uwaterloo_ca/Documents/Symbiosis Lab/Waqas/Side Projects/Bipartitie_3_way/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="496" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{420A9D7B-8483-BB4C-97A5-E07B8905E0F8}"/>
+  <xr:revisionPtr revIDLastSave="526" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC9F5465-1C10-4543-AA8C-126C3503A903}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="71">
   <si>
     <t>Communication</t>
   </si>
@@ -202,9 +202,6 @@
     <t>Studio Pedagogy</t>
   </si>
   <si>
-    <t>title</t>
-  </si>
-  <si>
     <t>Column Headers</t>
   </si>
   <si>
@@ -215,6 +212,45 @@
   </si>
   <si>
     <t>Critiques</t>
+  </si>
+  <si>
+    <t>Left Colors</t>
+  </si>
+  <si>
+    <t>FF0066</t>
+  </si>
+  <si>
+    <t>F0C800</t>
+  </si>
+  <si>
+    <t>FF9933</t>
+  </si>
+  <si>
+    <t>Mid Colors</t>
+  </si>
+  <si>
+    <t>0033CC</t>
+  </si>
+  <si>
+    <t>Right Colors</t>
+  </si>
+  <si>
+    <t>DDD9C3</t>
+  </si>
+  <si>
+    <t>C4BD97</t>
+  </si>
+  <si>
+    <t>948A54</t>
+  </si>
+  <si>
+    <t>79724f</t>
+  </si>
+  <si>
+    <t>4A452A</t>
+  </si>
+  <si>
+    <t>Title</t>
   </si>
 </sst>
 </file>
@@ -412,7 +448,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -624,6 +660,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -732,6 +779,19 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -750,17 +810,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -782,21 +869,18 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -806,25 +890,25 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -886,7 +970,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -925,32 +1009,32 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -962,7 +1046,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1024,7 +1108,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1037,37 +1121,54 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1495,141 +1596,141 @@
   <sheetData>
     <row r="3" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="14"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="16" t="s">
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="16" t="s">
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="17"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="16" t="s">
+      <c r="M4" s="15"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="18"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="16"/>
     </row>
     <row r="5" spans="2:27" ht="139.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="19"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="21" t="s">
+      <c r="L5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="23" t="s">
+      <c r="N5" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="21" t="s">
+      <c r="O5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P5" s="22" t="s">
+      <c r="P5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="Q5" s="22" t="s">
+      <c r="Q5" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="R5" s="23" t="s">
+      <c r="R5" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="S5" s="96" t="s">
+      <c r="S5" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="T5" s="109" t="s">
+      <c r="T5" s="105" t="s">
         <v>52</v>
       </c>
-      <c r="U5" s="109"/>
+      <c r="U5" s="105"/>
     </row>
     <row r="6" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q6" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="R6" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="S6" s="112">
+      <c r="D6" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="S6" s="106">
         <v>10</v>
       </c>
       <c r="T6">
@@ -1637,173 +1738,173 @@
       </c>
     </row>
     <row r="7" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="33"/>
-      <c r="C7" s="34" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="P7" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="R7" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="S7" s="112"/>
+      <c r="D7" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="106"/>
       <c r="T7">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="46"/>
-      <c r="C8" s="47" t="s">
+      <c r="B8" s="44"/>
+      <c r="C8" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="54" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="P8" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q8" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="R8" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="S8" s="112"/>
+      <c r="D8" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="R8" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="S8" s="106"/>
       <c r="T8">
         <v>50</v>
       </c>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
-      <c r="Y8" s="83"/>
-      <c r="Z8" s="84"/>
-      <c r="AA8" s="85"/>
+      <c r="Y8" s="81"/>
+      <c r="Z8" s="82"/>
+      <c r="AA8" s="83"/>
     </row>
     <row r="9" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="56" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="R9" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="S9" s="112">
+      <c r="D9" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="S9" s="106">
         <v>50</v>
       </c>
       <c r="T9">
@@ -1811,483 +1912,483 @@
       </c>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
-      <c r="Y9" s="86"/>
-      <c r="Z9" s="84"/>
-      <c r="AA9" s="87"/>
+      <c r="Y9" s="84"/>
+      <c r="Z9" s="82"/>
+      <c r="AA9" s="85"/>
     </row>
     <row r="10" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="33"/>
-      <c r="C10" s="34" t="s">
+      <c r="B10" s="31"/>
+      <c r="C10" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="P10" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q10" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="R10" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="S10" s="112"/>
+      <c r="D10" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="R10" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="S10" s="106"/>
       <c r="T10">
         <v>35</v>
       </c>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
-      <c r="Y10" s="88"/>
-      <c r="Z10" s="84"/>
-      <c r="AA10" s="89"/>
+      <c r="Y10" s="86"/>
+      <c r="Z10" s="82"/>
+      <c r="AA10" s="87"/>
     </row>
     <row r="11" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="33"/>
-      <c r="C11" s="34" t="s">
+      <c r="B11" s="31"/>
+      <c r="C11" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="O11" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q11" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="R11" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="S11" s="112"/>
+      <c r="D11" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="R11" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11" s="106"/>
       <c r="T11">
         <v>40</v>
       </c>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
-      <c r="Y11" s="90"/>
-      <c r="Z11" s="84"/>
-      <c r="AA11" s="91"/>
+      <c r="Y11" s="88"/>
+      <c r="Z11" s="82"/>
+      <c r="AA11" s="89"/>
     </row>
     <row r="12" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="46"/>
-      <c r="C12" s="47" t="s">
+      <c r="B12" s="44"/>
+      <c r="C12" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="54" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="58" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="O12" s="54" t="s">
-        <v>27</v>
-      </c>
-      <c r="P12" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q12" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R12" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="S12" s="112"/>
+      <c r="D12" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="R12" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="S12" s="106"/>
       <c r="T12">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="O13" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q13" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="R13" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="S13" s="112">
+      <c r="D13" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="57" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="57" t="s">
+        <v>25</v>
+      </c>
+      <c r="O13" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="R13" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="S13" s="106">
         <v>25</v>
       </c>
       <c r="T13">
         <v>20</v>
       </c>
-      <c r="Y13" s="92" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z13" s="77"/>
-      <c r="AA13" s="78" t="s">
+      <c r="Y13" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z13" s="75"/>
+      <c r="AA13" s="76" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="33"/>
-      <c r="C14" s="34" t="s">
+      <c r="B14" s="31"/>
+      <c r="C14" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="O14" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q14" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="R14" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="S14" s="112"/>
+      <c r="D14" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="O14" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="R14" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="S14" s="106"/>
       <c r="T14">
         <v>40</v>
       </c>
-      <c r="Y14" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z14" s="77"/>
-      <c r="AA14" s="80" t="s">
+      <c r="Y14" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z14" s="75"/>
+      <c r="AA14" s="78" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="33"/>
-      <c r="C15" s="34" t="s">
+      <c r="B15" s="31"/>
+      <c r="C15" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="N15" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="O15" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="P15" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q15" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="R15" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="S15" s="112"/>
+      <c r="D15" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="N15" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="R15" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="S15" s="106"/>
       <c r="T15">
         <v>25</v>
       </c>
-      <c r="Y15" s="81" t="s">
+      <c r="Y15" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="Z15" s="77"/>
-      <c r="AA15" s="82" t="s">
+      <c r="Z15" s="75"/>
+      <c r="AA15" s="80" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="2:27" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="60"/>
-      <c r="C16" s="61" t="s">
+      <c r="B16" s="58"/>
+      <c r="C16" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="J16" s="66" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" s="64" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="N16" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="O16" s="69" t="s">
-        <v>25</v>
-      </c>
-      <c r="P16" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q16" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="R16" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="S16" s="112"/>
+      <c r="D16" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="N16" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="O16" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="R16" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="S16" s="106"/>
       <c r="T16">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="N17" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="O17" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="P17" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q17" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="R17" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="S17" s="112">
+      <c r="D17" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="R17" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="S17" s="106">
         <v>15</v>
       </c>
       <c r="T17">
@@ -2295,197 +2396,197 @@
       </c>
     </row>
     <row r="18" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="70"/>
-      <c r="C18" s="34" t="s">
+      <c r="B18" s="68"/>
+      <c r="C18" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="J18" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="N18" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="O18" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="P18" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q18" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="R18" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="S18" s="112"/>
+      <c r="D18" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="O18" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="P18" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="R18" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18" s="106"/>
       <c r="T18">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="2:20" ht="17" x14ac:dyDescent="0.2">
-      <c r="B19" s="70"/>
-      <c r="C19" s="71" t="s">
+      <c r="B19" s="68"/>
+      <c r="C19" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="J19" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="L19" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="N19" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O19" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="P19" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="R19" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="S19" s="112"/>
+      <c r="D19" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="R19" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" s="106"/>
       <c r="T19">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="2:20" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="72"/>
-      <c r="C20" s="73" t="s">
+      <c r="B20" s="70"/>
+      <c r="C20" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="54" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="J20" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" s="76" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="O20" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="P20" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q20" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="R20" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="S20" s="112"/>
+      <c r="D20" s="72" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="O20" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="P20" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="R20" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="S20" s="106"/>
       <c r="T20">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="C21" s="98" t="s">
+      <c r="C21" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="113">
+      <c r="D21" s="107">
         <v>40</v>
       </c>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="113">
+      <c r="E21" s="107"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="107">
         <v>30</v>
       </c>
-      <c r="I21" s="113"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="113"/>
-      <c r="L21" s="113">
+      <c r="I21" s="107"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="107"/>
+      <c r="L21" s="107">
         <v>20</v>
       </c>
-      <c r="M21" s="113"/>
-      <c r="N21" s="113"/>
-      <c r="O21" s="113">
+      <c r="M21" s="107"/>
+      <c r="N21" s="107"/>
+      <c r="O21" s="107">
         <v>10</v>
       </c>
-      <c r="P21" s="113"/>
-      <c r="Q21" s="113"/>
-      <c r="R21" s="113"/>
+      <c r="P21" s="107"/>
+      <c r="Q21" s="107"/>
+      <c r="R21" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -2587,152 +2688,152 @@
     </row>
     <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="16" t="s">
+      <c r="B2" s="97"/>
+      <c r="C2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="16" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="16" t="s">
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="17"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="16" t="s">
+      <c r="L2" s="15"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="97" t="s">
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="95" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="131" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="101" t="str">
+      <c r="B3" s="111"/>
+      <c r="C3" s="98" t="str">
         <f>'Relationship Matrix'!D5</f>
         <v>Data integration</v>
       </c>
-      <c r="D3" s="101" t="str">
+      <c r="D3" s="98" t="str">
         <f>'Relationship Matrix'!E5</f>
         <v>Conceptual grounding</v>
       </c>
-      <c r="E3" s="101" t="str">
+      <c r="E3" s="98" t="str">
         <f>'Relationship Matrix'!F5</f>
         <v>Comparative learning</v>
       </c>
-      <c r="F3" s="101" t="str">
+      <c r="F3" s="98" t="str">
         <f>'Relationship Matrix'!G5</f>
         <v>Context mapping</v>
       </c>
-      <c r="G3" s="101" t="str">
+      <c r="G3" s="98" t="str">
         <f>'Relationship Matrix'!H5</f>
         <v>Functionality</v>
       </c>
-      <c r="H3" s="101" t="str">
+      <c r="H3" s="98" t="str">
         <f>'Relationship Matrix'!I5</f>
         <v>Aesthetics</v>
       </c>
-      <c r="I3" s="101" t="str">
+      <c r="I3" s="98" t="str">
         <f>'Relationship Matrix'!J5</f>
         <v>Social value &amp; wellbeing</v>
       </c>
-      <c r="J3" s="101" t="str">
+      <c r="J3" s="98" t="str">
         <f>'Relationship Matrix'!K5</f>
         <v>Assembly resolution</v>
       </c>
-      <c r="K3" s="101" t="str">
+      <c r="K3" s="98" t="str">
         <f>'Relationship Matrix'!L5</f>
         <v>Cost estimate</v>
       </c>
-      <c r="L3" s="101" t="str">
+      <c r="L3" s="98" t="str">
         <f>'Relationship Matrix'!M5</f>
         <v>Code compliance</v>
       </c>
-      <c r="M3" s="101" t="str">
+      <c r="M3" s="98" t="str">
         <f>'Relationship Matrix'!N5</f>
         <v>Environmental impact</v>
       </c>
-      <c r="N3" s="101" t="str">
+      <c r="N3" s="98" t="str">
         <f>'Relationship Matrix'!O5</f>
         <v>Structured narrative</v>
       </c>
-      <c r="O3" s="101" t="str">
+      <c r="O3" s="98" t="str">
         <f>'Relationship Matrix'!P5</f>
         <v>Collaborative dialogue</v>
       </c>
-      <c r="P3" s="101" t="str">
+      <c r="P3" s="98" t="str">
         <f>'Relationship Matrix'!Q5</f>
         <v>Completeness</v>
       </c>
-      <c r="Q3" s="101" t="str">
+      <c r="Q3" s="98" t="str">
         <f>'Relationship Matrix'!R5</f>
         <v>Standards &amp; conventions</v>
       </c>
-      <c r="R3" s="94"/>
+      <c r="R3" s="92"/>
     </row>
     <row r="4" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>0</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="112" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="93" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="R4" s="94">
+      <c r="C4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="91" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="R4" s="92">
         <v>40</v>
       </c>
     </row>
@@ -2740,55 +2841,55 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="107" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="R5" s="94">
+      <c r="C5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="104" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="91" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="R5" s="92">
         <v>25</v>
       </c>
     </row>
@@ -2796,55 +2897,55 @@
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="93" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="R6" s="94">
+      <c r="C6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="91" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" s="92">
         <v>15</v>
       </c>
     </row>
@@ -2852,55 +2953,55 @@
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="114" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="R7" s="94">
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="92">
         <v>10</v>
       </c>
     </row>
@@ -2908,133 +3009,133 @@
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="R8" s="94">
+      <c r="C8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="R8" s="92">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="102">
+      <c r="C9" s="99">
         <v>20</v>
       </c>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="102">
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="99">
         <v>40</v>
       </c>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="102">
-        <v>25</v>
-      </c>
-      <c r="L9" s="95"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="102">
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="99">
+        <v>25</v>
+      </c>
+      <c r="L9" s="93"/>
+      <c r="M9" s="100"/>
+      <c r="N9" s="99">
         <v>15</v>
       </c>
-      <c r="O9" s="95"/>
-      <c r="P9" s="95"/>
-      <c r="Q9" s="103"/>
+      <c r="O9" s="93"/>
+      <c r="P9" s="93"/>
+      <c r="Q9" s="100"/>
     </row>
     <row r="10" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="108" t="s">
+      <c r="B10" s="116" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="104">
+      <c r="C10" s="101">
         <v>20</v>
       </c>
-      <c r="D10" s="105">
+      <c r="D10" s="102">
         <v>30</v>
       </c>
-      <c r="E10" s="105">
+      <c r="E10" s="102">
         <v>15</v>
       </c>
-      <c r="F10" s="106">
+      <c r="F10" s="103">
         <v>35</v>
       </c>
-      <c r="G10" s="104">
-        <v>25</v>
-      </c>
-      <c r="H10" s="105">
+      <c r="G10" s="101">
+        <v>25</v>
+      </c>
+      <c r="H10" s="102">
         <v>30</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="102">
         <v>30</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="103">
         <v>15</v>
       </c>
-      <c r="K10" s="104">
+      <c r="K10" s="101">
         <v>50</v>
       </c>
-      <c r="L10" s="105">
+      <c r="L10" s="102">
         <v>30</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="103">
         <v>20</v>
       </c>
-      <c r="N10" s="104">
+      <c r="N10" s="101">
         <v>35</v>
       </c>
-      <c r="O10" s="105">
-        <v>25</v>
-      </c>
-      <c r="P10" s="105">
-        <v>25</v>
-      </c>
-      <c r="Q10" s="106">
+      <c r="O10" s="102">
+        <v>25</v>
+      </c>
+      <c r="P10" s="102">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="103">
         <v>15</v>
       </c>
     </row>
@@ -3070,7 +3171,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC3B74E4-6D3C-A34A-BD08-E56EF3EFCE42}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -3078,26 +3179,88 @@
     <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="110" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="108" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="111" t="s">
-        <v>53</v>
-      </c>
+      <c r="B2" s="110" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="110" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="110" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="110" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="108" t="s">
         <v>58</v>
+      </c>
+      <c r="B3" s="110">
+        <v>663366</v>
+      </c>
+      <c r="C3" s="110" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="110" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="110" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="110"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="108" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="110">
+        <v>339966</v>
+      </c>
+      <c r="D4" s="110">
+        <v>339999</v>
+      </c>
+      <c r="E4" s="110">
+        <v>666699</v>
+      </c>
+      <c r="F4" s="110"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="110" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="110" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="110" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="110" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Required weights.xlsx
+++ b/Required weights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofwaterloo-my.sharepoint.com/personal/maraji_uwaterloo_ca/Documents/Symbiosis Lab/Waqas/Side Projects/Bipartitie_3_way/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="526" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC9F5465-1C10-4543-AA8C-126C3503A903}"/>
+  <xr:revisionPtr revIDLastSave="532" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{995DC232-A255-A44E-A0C6-20861DB0A227}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12620" yWindow="660" windowWidth="17620" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relationship Matrix" sheetId="7" r:id="rId1"/>
@@ -844,7 +844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -875,27 +875,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
@@ -905,9 +884,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -932,7 +908,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -969,7 +944,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1009,7 +983,6 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1037,14 +1010,8 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1074,29 +1041,28 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1106,9 +1072,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1123,12 +1086,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -1136,19 +1093,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1169,54 +1117,60 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1596,141 +1550,141 @@
   <sheetData>
     <row r="3" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14" t="s">
+      <c r="B4" s="108"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="14" t="s">
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="14" t="s">
+      <c r="I4" s="100"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="15"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="14" t="s">
+      <c r="M4" s="100"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="16"/>
+      <c r="P4" s="100"/>
+      <c r="Q4" s="100"/>
+      <c r="R4" s="101"/>
     </row>
     <row r="5" spans="2:27" ht="139.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="19" t="s">
+      <c r="B5" s="110"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="21" t="s">
+      <c r="K5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="20" t="s">
+      <c r="M5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="21" t="s">
+      <c r="N5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="19" t="s">
+      <c r="O5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="P5" s="20" t="s">
+      <c r="P5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Q5" s="20" t="s">
+      <c r="Q5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="R5" s="21" t="s">
+      <c r="R5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="S5" s="94" t="s">
+      <c r="S5" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="T5" s="105" t="s">
+      <c r="T5" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="U5" s="105"/>
+      <c r="U5" s="88"/>
     </row>
     <row r="6" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q6" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="R6" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="S6" s="106">
+      <c r="D6" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="S6" s="97">
         <v>10</v>
       </c>
       <c r="T6">
@@ -1738,173 +1692,172 @@
       </c>
     </row>
     <row r="7" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="31"/>
-      <c r="C7" s="32" t="s">
+      <c r="B7" s="103"/>
+      <c r="C7" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="P7" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="R7" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="S7" s="106"/>
+      <c r="D7" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="97"/>
       <c r="T7">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="44"/>
-      <c r="C8" s="45" t="s">
+      <c r="B8" s="104"/>
+      <c r="C8" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="P8" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q8" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="R8" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="S8" s="106"/>
+      <c r="D8" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="R8" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="S8" s="97"/>
       <c r="T8">
         <v>50</v>
       </c>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
-      <c r="Y8" s="81"/>
-      <c r="Z8" s="82"/>
-      <c r="AA8" s="83"/>
+      <c r="Y8" s="68"/>
+      <c r="AA8" s="69"/>
     </row>
     <row r="9" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="54" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="P9" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="R9" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="S9" s="106">
+      <c r="D9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="S9" s="97">
         <v>50</v>
       </c>
       <c r="T9">
@@ -1912,483 +1865,480 @@
       </c>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
-      <c r="Y9" s="84"/>
-      <c r="Z9" s="82"/>
-      <c r="AA9" s="85"/>
+      <c r="Y9" s="70"/>
+      <c r="AA9" s="71"/>
     </row>
     <row r="10" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="31"/>
-      <c r="C10" s="32" t="s">
+      <c r="B10" s="103"/>
+      <c r="C10" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="P10" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q10" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="R10" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="S10" s="106"/>
+      <c r="D10" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="R10" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="S10" s="97"/>
       <c r="T10">
         <v>35</v>
       </c>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
-      <c r="Y10" s="86"/>
-      <c r="Z10" s="82"/>
-      <c r="AA10" s="87"/>
+      <c r="Y10" s="72"/>
+      <c r="AA10" s="73"/>
     </row>
     <row r="11" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="31"/>
-      <c r="C11" s="32" t="s">
+      <c r="B11" s="103"/>
+      <c r="C11" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="O11" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q11" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="R11" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="S11" s="106"/>
+      <c r="D11" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="R11" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11" s="97"/>
       <c r="T11">
         <v>40</v>
       </c>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
-      <c r="Y11" s="88"/>
-      <c r="Z11" s="82"/>
-      <c r="AA11" s="89"/>
+      <c r="Y11" s="74"/>
+      <c r="AA11" s="75"/>
     </row>
     <row r="12" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="44"/>
-      <c r="C12" s="45" t="s">
+      <c r="B12" s="104"/>
+      <c r="C12" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="56" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="O12" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="P12" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q12" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="R12" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="S12" s="106"/>
+      <c r="D12" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="R12" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="S12" s="97"/>
       <c r="T12">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="O13" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q13" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="R13" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="S13" s="106">
+      <c r="D13" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="O13" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="R13" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="S13" s="97">
         <v>25</v>
       </c>
       <c r="T13">
         <v>20</v>
       </c>
-      <c r="Y13" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z13" s="75"/>
-      <c r="AA13" s="76" t="s">
+      <c r="Y13" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z13" s="62"/>
+      <c r="AA13" s="63" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="31"/>
-      <c r="C14" s="32" t="s">
+      <c r="B14" s="103"/>
+      <c r="C14" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="O14" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q14" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="R14" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="S14" s="106"/>
+      <c r="D14" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="O14" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="R14" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="S14" s="97"/>
       <c r="T14">
         <v>40</v>
       </c>
-      <c r="Y14" s="77" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z14" s="75"/>
-      <c r="AA14" s="78" t="s">
+      <c r="Y14" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z14" s="62"/>
+      <c r="AA14" s="65" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="31"/>
-      <c r="C15" s="32" t="s">
+      <c r="B15" s="103"/>
+      <c r="C15" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="N15" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="O15" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="P15" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q15" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="R15" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="S15" s="106"/>
+      <c r="D15" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="N15" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="R15" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="S15" s="97"/>
       <c r="T15">
         <v>25</v>
       </c>
-      <c r="Y15" s="79" t="s">
+      <c r="Y15" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="Z15" s="75"/>
-      <c r="AA15" s="80" t="s">
+      <c r="Z15" s="62"/>
+      <c r="AA15" s="67" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="2:27" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="58"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="105"/>
+      <c r="C16" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="J16" s="64" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" s="63" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="N16" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="O16" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="P16" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q16" s="64" t="s">
-        <v>26</v>
-      </c>
-      <c r="R16" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="S16" s="106"/>
+      <c r="D16" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="N16" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="O16" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="R16" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="S16" s="97"/>
       <c r="T16">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="N17" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="O17" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="P17" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q17" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="R17" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="S17" s="106">
+      <c r="D17" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="R17" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="S17" s="97">
         <v>15</v>
       </c>
       <c r="T17">
@@ -2396,200 +2346,209 @@
       </c>
     </row>
     <row r="18" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="68"/>
-      <c r="C18" s="32" t="s">
+      <c r="B18" s="106"/>
+      <c r="C18" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="I18" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="J18" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="N18" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="O18" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="P18" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q18" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="R18" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="S18" s="106"/>
+      <c r="D18" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="O18" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="P18" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="R18" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18" s="97"/>
       <c r="T18">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="2:20" ht="17" x14ac:dyDescent="0.2">
-      <c r="B19" s="68"/>
-      <c r="C19" s="69" t="s">
+      <c r="B19" s="106"/>
+      <c r="C19" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="J19" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="L19" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="N19" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="O19" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="P19" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="R19" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="S19" s="106"/>
+      <c r="D19" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="R19" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" s="97"/>
       <c r="T19">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="2:20" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="70"/>
-      <c r="C20" s="71" t="s">
+      <c r="B20" s="107"/>
+      <c r="C20" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="J20" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" s="73" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" s="74" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="O20" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="P20" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q20" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="R20" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="S20" s="106"/>
+      <c r="D20" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="O20" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="P20" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="R20" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="S20" s="97"/>
       <c r="T20">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="C21" s="96" t="s">
+      <c r="C21" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="107">
+      <c r="D21" s="98">
         <v>40</v>
       </c>
-      <c r="E21" s="107"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="107"/>
-      <c r="H21" s="107">
+      <c r="E21" s="98"/>
+      <c r="F21" s="98"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="98">
         <v>30</v>
       </c>
-      <c r="I21" s="107"/>
-      <c r="J21" s="107"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="107">
+      <c r="I21" s="98"/>
+      <c r="J21" s="98"/>
+      <c r="K21" s="98"/>
+      <c r="L21" s="98">
         <v>20</v>
       </c>
-      <c r="M21" s="107"/>
-      <c r="N21" s="107"/>
-      <c r="O21" s="107">
+      <c r="M21" s="98"/>
+      <c r="N21" s="98"/>
+      <c r="O21" s="98">
         <v>10</v>
       </c>
-      <c r="P21" s="107"/>
-      <c r="Q21" s="107"/>
-      <c r="R21" s="107"/>
+      <c r="P21" s="98"/>
+      <c r="Q21" s="98"/>
+      <c r="R21" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="L4:N4"/>
     <mergeCell ref="S6:S8"/>
     <mergeCell ref="S9:S12"/>
     <mergeCell ref="S13:S16"/>
@@ -2598,27 +2557,18 @@
     <mergeCell ref="H21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:R21"/>
-    <mergeCell ref="O4:R4"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B4:C5"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:R20">
-    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="W">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="W">
       <formula>NOT(ISERROR(SEARCH("W",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="S">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="S">
       <formula>NOT(ISERROR(SEARCH("S",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="N">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="N">
       <formula>NOT(ISERROR(SEARCH("N",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2688,104 +2638,104 @@
     </row>
     <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="82"/>
+      <c r="C2" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="14" t="s">
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="14" t="s">
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="15"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="14" t="s">
+      <c r="L2" s="100"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="95" t="s">
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="80" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="111"/>
-      <c r="C3" s="98" t="str">
+      <c r="B3" s="91"/>
+      <c r="C3" s="83" t="str">
         <f>'Relationship Matrix'!D5</f>
         <v>Data integration</v>
       </c>
-      <c r="D3" s="98" t="str">
+      <c r="D3" s="83" t="str">
         <f>'Relationship Matrix'!E5</f>
         <v>Conceptual grounding</v>
       </c>
-      <c r="E3" s="98" t="str">
+      <c r="E3" s="83" t="str">
         <f>'Relationship Matrix'!F5</f>
         <v>Comparative learning</v>
       </c>
-      <c r="F3" s="98" t="str">
+      <c r="F3" s="83" t="str">
         <f>'Relationship Matrix'!G5</f>
         <v>Context mapping</v>
       </c>
-      <c r="G3" s="98" t="str">
+      <c r="G3" s="83" t="str">
         <f>'Relationship Matrix'!H5</f>
         <v>Functionality</v>
       </c>
-      <c r="H3" s="98" t="str">
+      <c r="H3" s="83" t="str">
         <f>'Relationship Matrix'!I5</f>
         <v>Aesthetics</v>
       </c>
-      <c r="I3" s="98" t="str">
+      <c r="I3" s="83" t="str">
         <f>'Relationship Matrix'!J5</f>
         <v>Social value &amp; wellbeing</v>
       </c>
-      <c r="J3" s="98" t="str">
+      <c r="J3" s="83" t="str">
         <f>'Relationship Matrix'!K5</f>
         <v>Assembly resolution</v>
       </c>
-      <c r="K3" s="98" t="str">
+      <c r="K3" s="83" t="str">
         <f>'Relationship Matrix'!L5</f>
         <v>Cost estimate</v>
       </c>
-      <c r="L3" s="98" t="str">
+      <c r="L3" s="83" t="str">
         <f>'Relationship Matrix'!M5</f>
         <v>Code compliance</v>
       </c>
-      <c r="M3" s="98" t="str">
+      <c r="M3" s="83" t="str">
         <f>'Relationship Matrix'!N5</f>
         <v>Environmental impact</v>
       </c>
-      <c r="N3" s="98" t="str">
+      <c r="N3" s="83" t="str">
         <f>'Relationship Matrix'!O5</f>
         <v>Structured narrative</v>
       </c>
-      <c r="O3" s="98" t="str">
+      <c r="O3" s="83" t="str">
         <f>'Relationship Matrix'!P5</f>
         <v>Collaborative dialogue</v>
       </c>
-      <c r="P3" s="98" t="str">
+      <c r="P3" s="83" t="str">
         <f>'Relationship Matrix'!Q5</f>
         <v>Completeness</v>
       </c>
-      <c r="Q3" s="98" t="str">
+      <c r="Q3" s="83" t="str">
         <f>'Relationship Matrix'!R5</f>
         <v>Standards &amp; conventions</v>
       </c>
-      <c r="R3" s="92"/>
+      <c r="R3" s="78"/>
     </row>
     <row r="4" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>0</v>
       </c>
-      <c r="B4" s="112" t="s">
+      <c r="B4" s="92" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="8" t="s">
@@ -2812,10 +2762,10 @@
       <c r="J4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="91" t="s">
+      <c r="K4" s="87" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="77" t="s">
         <v>26</v>
       </c>
       <c r="M4" s="6" t="s">
@@ -2833,7 +2783,7 @@
       <c r="Q4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="R4" s="92">
+      <c r="R4" s="78">
         <v>40</v>
       </c>
     </row>
@@ -2841,7 +2791,7 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="113" t="s">
+      <c r="B5" s="93" t="s">
         <v>47</v>
       </c>
       <c r="C5" s="10" t="s">
@@ -2868,10 +2818,10 @@
       <c r="J5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="104" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="91" t="s">
+      <c r="K5" s="87" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="77" t="s">
         <v>25</v>
       </c>
       <c r="M5" s="9" t="s">
@@ -2889,7 +2839,7 @@
       <c r="Q5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="R5" s="92">
+      <c r="R5" s="78">
         <v>25</v>
       </c>
     </row>
@@ -2897,7 +2847,7 @@
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="113" t="s">
+      <c r="B6" s="93" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -2924,10 +2874,10 @@
       <c r="J6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="91" t="s">
+      <c r="K6" s="87" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="77" t="s">
         <v>26</v>
       </c>
       <c r="M6" s="9" t="s">
@@ -2945,7 +2895,7 @@
       <c r="Q6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="R6" s="92">
+      <c r="R6" s="78">
         <v>15</v>
       </c>
     </row>
@@ -2953,7 +2903,7 @@
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="114" t="s">
+      <c r="B7" s="94" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -3001,7 +2951,7 @@
       <c r="Q7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="R7" s="92">
+      <c r="R7" s="78">
         <v>10</v>
       </c>
     </row>
@@ -3009,41 +2959,41 @@
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="113" t="s">
+      <c r="B8" s="93" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>25</v>
+      <c r="F8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>25</v>
+      <c r="L8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>25</v>
@@ -3057,85 +3007,85 @@
       <c r="Q8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="R8" s="92">
+      <c r="R8" s="78">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="B9" s="115" t="s">
+      <c r="B9" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="99">
+      <c r="C9" s="112">
         <v>20</v>
       </c>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="99">
+      <c r="D9" s="113"/>
+      <c r="E9" s="113"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="112">
         <v>40</v>
       </c>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="100"/>
-      <c r="K9" s="99">
-        <v>25</v>
-      </c>
-      <c r="L9" s="93"/>
-      <c r="M9" s="100"/>
-      <c r="N9" s="99">
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
+      <c r="J9" s="114"/>
+      <c r="K9" s="112">
+        <v>25</v>
+      </c>
+      <c r="L9" s="113"/>
+      <c r="M9" s="114"/>
+      <c r="N9" s="112">
         <v>15</v>
       </c>
-      <c r="O9" s="93"/>
-      <c r="P9" s="93"/>
-      <c r="Q9" s="100"/>
+      <c r="O9" s="113"/>
+      <c r="P9" s="113"/>
+      <c r="Q9" s="114"/>
     </row>
     <row r="10" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="116" t="s">
+      <c r="B10" s="96" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="101">
+      <c r="C10" s="84">
         <v>20</v>
       </c>
-      <c r="D10" s="102">
+      <c r="D10" s="85">
         <v>30</v>
       </c>
-      <c r="E10" s="102">
+      <c r="E10" s="85">
         <v>15</v>
       </c>
-      <c r="F10" s="103">
+      <c r="F10" s="86">
         <v>35</v>
       </c>
-      <c r="G10" s="101">
-        <v>25</v>
-      </c>
-      <c r="H10" s="102">
+      <c r="G10" s="84">
+        <v>25</v>
+      </c>
+      <c r="H10" s="85">
         <v>30</v>
       </c>
-      <c r="I10" s="102">
+      <c r="I10" s="85">
         <v>30</v>
       </c>
-      <c r="J10" s="103">
+      <c r="J10" s="86">
         <v>15</v>
       </c>
-      <c r="K10" s="101">
+      <c r="K10" s="84">
         <v>50</v>
       </c>
-      <c r="L10" s="102">
+      <c r="L10" s="85">
         <v>30</v>
       </c>
-      <c r="M10" s="103">
+      <c r="M10" s="86">
         <v>20</v>
       </c>
-      <c r="N10" s="101">
+      <c r="N10" s="84">
         <v>35</v>
       </c>
-      <c r="O10" s="102">
-        <v>25</v>
-      </c>
-      <c r="P10" s="102">
-        <v>25</v>
-      </c>
-      <c r="Q10" s="103">
+      <c r="O10" s="85">
+        <v>25</v>
+      </c>
+      <c r="P10" s="85">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="86">
         <v>15</v>
       </c>
     </row>
@@ -3180,86 +3130,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="89" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="89" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="110" t="s">
+      <c r="C2" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="110" t="s">
+      <c r="D2" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="110">
+      <c r="B3" s="90">
         <v>663366</v>
       </c>
-      <c r="C3" s="110" t="s">
+      <c r="C3" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="110" t="s">
+      <c r="D3" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="110" t="s">
+      <c r="E3" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="110"/>
+      <c r="F3" s="90"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="90" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="110">
+      <c r="C4" s="90">
         <v>339966</v>
       </c>
-      <c r="D4" s="110">
+      <c r="D4" s="90">
         <v>339999</v>
       </c>
-      <c r="E4" s="110">
+      <c r="E4" s="90">
         <v>666699</v>
       </c>
-      <c r="F4" s="110"/>
+      <c r="F4" s="90"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="110" t="s">
+      <c r="C5" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="110" t="s">
+      <c r="D5" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="110" t="s">
+      <c r="E5" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="110" t="s">
+      <c r="F5" s="90" t="s">
         <v>69</v>
       </c>
     </row>

--- a/Required weights.xlsx
+++ b/Required weights.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofwaterloo-my.sharepoint.com/personal/maraji_uwaterloo_ca/Documents/Symbiosis Lab/Waqas/Side Projects/Bipartitie_3_way/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="532" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{995DC232-A255-A44E-A0C6-20861DB0A227}"/>
+  <xr:revisionPtr revIDLastSave="541" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D73CFDE2-9A37-734D-BFCF-4FD5FFBB2A27}"/>
   <bookViews>
     <workbookView xWindow="12620" yWindow="660" windowWidth="17620" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2966,34 +2966,34 @@
         <v>27</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>26</v>
+      <c r="F8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>26</v>
+      <c r="L8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>25</v>

--- a/Required weights.xlsx
+++ b/Required weights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofwaterloo-my.sharepoint.com/personal/maraji_uwaterloo_ca/Documents/Symbiosis Lab/Waqas/Side Projects/Bipartitie_3_way/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="541" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D73CFDE2-9A37-734D-BFCF-4FD5FFBB2A27}"/>
+  <xr:revisionPtr revIDLastSave="547" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC6FA62B-510C-0C4C-B0A5-17ECE172735D}"/>
   <bookViews>
-    <workbookView xWindow="12620" yWindow="660" windowWidth="17620" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1940" yWindow="-18880" windowWidth="17620" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relationship Matrix" sheetId="7" r:id="rId1"/>
@@ -2966,40 +2966,40 @@
         <v>27</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>25</v>
+      <c r="F8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>25</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P8" s="4" t="s">
         <v>25</v>

--- a/Required weights.xlsx
+++ b/Required weights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofwaterloo-my.sharepoint.com/personal/maraji_uwaterloo_ca/Documents/Symbiosis Lab/Waqas/Side Projects/Bipartitie_3_way/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="547" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC6FA62B-510C-0C4C-B0A5-17ECE172735D}"/>
+  <xr:revisionPtr revIDLastSave="553" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DA25437-D0C9-1E4B-AFA3-E89901CAC6D5}"/>
   <bookViews>
-    <workbookView xWindow="-1940" yWindow="-18880" windowWidth="17620" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1940" yWindow="-18880" windowWidth="24080" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relationship Matrix" sheetId="7" r:id="rId1"/>
@@ -76,9 +76,6 @@
     <t>Structured narrative</t>
   </si>
   <si>
-    <t>Conceptual grounding</t>
-  </si>
-  <si>
     <t>Aesthetics</t>
   </si>
   <si>
@@ -205,15 +202,6 @@
     <t>Column Headers</t>
   </si>
   <si>
-    <t>Methods</t>
-  </si>
-  <si>
-    <t>Learning outcomes</t>
-  </si>
-  <si>
-    <t>Critiques</t>
-  </si>
-  <si>
     <t>Left Colors</t>
   </si>
   <si>
@@ -251,15 +239,34 @@
   </si>
   <si>
     <t>Title</t>
+  </si>
+  <si>
+    <t>Rationale</t>
+  </si>
+  <si>
+    <t>Learning modes</t>
+  </si>
+  <si>
+    <t>Process</t>
+  </si>
+  <si>
+    <t>Criteria</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -844,210 +851,204 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1065,97 +1066,64 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1165,6 +1133,48 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1550,141 +1560,141 @@
   <sheetData>
     <row r="3" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="108"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="99" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="99" t="s">
+      <c r="B4" s="106"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="100" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="100" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="100"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="101"/>
-      <c r="L4" s="99" t="s">
+      <c r="M4" s="101"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="100"/>
-      <c r="N4" s="101"/>
-      <c r="O4" s="99" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" s="100"/>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="101"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="102"/>
     </row>
     <row r="5" spans="2:27" ht="139.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="110"/>
-      <c r="C5" s="111"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="109"/>
       <c r="D5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>12</v>
+      <c r="E5" s="115" t="s">
+        <v>67</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K5" s="14" t="s">
         <v>10</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M5" s="13" t="s">
         <v>6</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O5" s="12" t="s">
         <v>11</v>
       </c>
       <c r="P5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Q5" s="13" t="s">
-        <v>16</v>
-      </c>
       <c r="R5" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S5" s="79" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T5" s="88" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U5" s="88"/>
     </row>
     <row r="6" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="103" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O6" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q6" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R6" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="S6" s="97">
+        <v>26</v>
+      </c>
+      <c r="S6" s="113">
         <v>10</v>
       </c>
       <c r="T6">
@@ -1692,111 +1702,111 @@
       </c>
     </row>
     <row r="7" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="103"/>
+      <c r="B7" s="110"/>
       <c r="C7" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K7" s="29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L7" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M7" s="31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O7" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P7" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q7" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R7" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="S7" s="97"/>
+        <v>26</v>
+      </c>
+      <c r="S7" s="113"/>
       <c r="T7">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="104"/>
+      <c r="B8" s="111"/>
       <c r="C8" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H8" s="36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" s="40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K8" s="41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L8" s="42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M8" s="40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N8" s="39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O8" s="42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P8" s="38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q8" s="38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R8" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="S8" s="97"/>
+        <v>26</v>
+      </c>
+      <c r="S8" s="113"/>
       <c r="T8">
         <v>50</v>
       </c>
@@ -1806,58 +1816,58 @@
       <c r="AA8" s="69"/>
     </row>
     <row r="9" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="103" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K9" s="43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M9" s="45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O9" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P9" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q9" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R9" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="S9" s="97">
+        <v>26</v>
+      </c>
+      <c r="S9" s="113">
         <v>50</v>
       </c>
       <c r="T9">
@@ -1869,56 +1879,56 @@
       <c r="AA9" s="71"/>
     </row>
     <row r="10" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="103"/>
+      <c r="B10" s="110"/>
       <c r="C10" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K10" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L10" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M10" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N10" s="27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P10" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q10" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R10" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="S10" s="97"/>
+        <v>26</v>
+      </c>
+      <c r="S10" s="113"/>
       <c r="T10">
         <v>35</v>
       </c>
@@ -1928,56 +1938,56 @@
       <c r="AA10" s="73"/>
     </row>
     <row r="11" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="103"/>
+      <c r="B11" s="110"/>
       <c r="C11" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J11" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L11" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M11" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N11" s="32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O11" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P11" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q11" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R11" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="S11" s="97"/>
+        <v>24</v>
+      </c>
+      <c r="S11" s="113"/>
       <c r="T11">
         <v>40</v>
       </c>
@@ -1987,358 +1997,358 @@
       <c r="AA11" s="75"/>
     </row>
     <row r="12" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="104"/>
+      <c r="B12" s="111"/>
       <c r="C12" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J12" s="40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K12" s="46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L12" s="42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N12" s="41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O12" s="42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P12" s="38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q12" s="40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R12" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="S12" s="97"/>
+        <v>26</v>
+      </c>
+      <c r="S12" s="113"/>
       <c r="T12">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="103" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K13" s="47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M13" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N13" s="47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P13" s="22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R13" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="S13" s="97">
+        <v>25</v>
+      </c>
+      <c r="S13" s="113">
         <v>25</v>
       </c>
       <c r="T13">
         <v>20</v>
       </c>
       <c r="Y13" s="76" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z13" s="62"/>
       <c r="AA13" s="63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="103"/>
+      <c r="B14" s="110"/>
       <c r="C14" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K14" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L14" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M14" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N14" s="32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O14" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P14" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q14" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R14" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="S14" s="97"/>
+        <v>26</v>
+      </c>
+      <c r="S14" s="113"/>
       <c r="T14">
         <v>40</v>
       </c>
       <c r="Y14" s="64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z14" s="62"/>
       <c r="AA14" s="65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="103"/>
+      <c r="B15" s="110"/>
       <c r="C15" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H15" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J15" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K15" s="32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L15" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M15" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N15" s="32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O15" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P15" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q15" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R15" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="S15" s="97"/>
+        <v>26</v>
+      </c>
+      <c r="S15" s="113"/>
       <c r="T15">
         <v>25</v>
       </c>
       <c r="Y15" s="66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z15" s="62"/>
       <c r="AA15" s="67" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="2:27" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="105"/>
+      <c r="B16" s="112"/>
       <c r="C16" s="48" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G16" s="51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H16" s="52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I16" s="50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J16" s="53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K16" s="51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L16" s="52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M16" s="54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N16" s="55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O16" s="56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P16" s="50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q16" s="53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R16" s="55" t="s">
-        <v>25</v>
-      </c>
-      <c r="S16" s="97"/>
+        <v>24</v>
+      </c>
+      <c r="S16" s="113"/>
       <c r="T16">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="102" t="s">
+      <c r="B17" s="103" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K17" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M17" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N17" s="43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O17" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q17" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R17" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="S17" s="97">
+        <v>26</v>
+      </c>
+      <c r="S17" s="113">
         <v>15</v>
       </c>
       <c r="T17">
@@ -2346,200 +2356,208 @@
       </c>
     </row>
     <row r="18" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="106"/>
+      <c r="B18" s="104"/>
       <c r="C18" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G18" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H18" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K18" s="32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M18" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N18" s="32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O18" s="33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P18" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q18" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R18" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="S18" s="97"/>
+        <v>24</v>
+      </c>
+      <c r="S18" s="113"/>
       <c r="T18">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="2:20" ht="17" x14ac:dyDescent="0.2">
-      <c r="B19" s="106"/>
+      <c r="B19" s="104"/>
       <c r="C19" s="57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" s="32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" s="33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L19" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M19" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N19" s="32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O19" s="33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P19" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q19" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R19" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="S19" s="97"/>
+        <v>26</v>
+      </c>
+      <c r="S19" s="113"/>
       <c r="T19">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="2:20" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
+      <c r="B20" s="105"/>
       <c r="C20" s="58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G20" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H20" s="42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I20" s="40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J20" s="40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K20" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L20" s="60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M20" s="61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N20" s="41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O20" s="36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P20" s="37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q20" s="37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R20" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="S20" s="97"/>
+        <v>26</v>
+      </c>
+      <c r="S20" s="113"/>
       <c r="T20">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C21" s="81" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="98">
+        <v>48</v>
+      </c>
+      <c r="D21" s="114">
         <v>40</v>
       </c>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="98">
+      <c r="E21" s="114"/>
+      <c r="F21" s="114"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="114">
         <v>30</v>
       </c>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98">
+      <c r="I21" s="114"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="114">
         <v>20</v>
       </c>
-      <c r="M21" s="98"/>
-      <c r="N21" s="98"/>
-      <c r="O21" s="98">
+      <c r="M21" s="114"/>
+      <c r="N21" s="114"/>
+      <c r="O21" s="114">
         <v>10</v>
       </c>
-      <c r="P21" s="98"/>
-      <c r="Q21" s="98"/>
-      <c r="R21" s="98"/>
+      <c r="P21" s="114"/>
+      <c r="Q21" s="114"/>
+      <c r="R21" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="S9:S12"/>
+    <mergeCell ref="S13:S16"/>
+    <mergeCell ref="S17:S20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:R21"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="B4:C5"/>
     <mergeCell ref="O4:R4"/>
@@ -2549,14 +2567,6 @@
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="L4:N4"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="S9:S12"/>
-    <mergeCell ref="S13:S16"/>
-    <mergeCell ref="S17:S20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:R21"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:R20">
     <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="M">
@@ -2639,31 +2649,31 @@
     <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="82"/>
-      <c r="C2" s="99" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="99" t="s">
+      <c r="C2" s="100" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="100" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="99" t="s">
+      <c r="L2" s="101"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="100"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="99" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="100"/>
-      <c r="P2" s="100"/>
-      <c r="Q2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="102"/>
       <c r="R2" s="80" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2675,7 +2685,7 @@
       </c>
       <c r="D3" s="83" t="str">
         <f>'Relationship Matrix'!E5</f>
-        <v>Conceptual grounding</v>
+        <v>Rationale</v>
       </c>
       <c r="E3" s="83" t="str">
         <f>'Relationship Matrix'!F5</f>
@@ -2736,52 +2746,52 @@
         <v>0</v>
       </c>
       <c r="B4" s="92" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K4" s="87" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L4" s="77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R4" s="78">
         <v>40</v>
@@ -2792,52 +2802,52 @@
         <v>1</v>
       </c>
       <c r="B5" s="93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" s="87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L5" s="77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R5" s="78">
         <v>25</v>
@@ -2848,52 +2858,52 @@
         <v>2</v>
       </c>
       <c r="B6" s="93" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" s="87" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L6" s="77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R6" s="78">
         <v>15</v>
@@ -2904,52 +2914,52 @@
         <v>3</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R7" s="78">
         <v>10</v>
@@ -2960,52 +2970,52 @@
         <v>4</v>
       </c>
       <c r="B8" s="93" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R8" s="78">
         <v>10</v>
@@ -3013,35 +3023,35 @@
     </row>
     <row r="9" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" s="95" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="112">
+        <v>48</v>
+      </c>
+      <c r="C9" s="97">
         <v>20</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="113"/>
-      <c r="F9" s="114"/>
-      <c r="G9" s="112">
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="97">
         <v>40</v>
       </c>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="114"/>
-      <c r="K9" s="112">
-        <v>25</v>
-      </c>
-      <c r="L9" s="113"/>
-      <c r="M9" s="114"/>
-      <c r="N9" s="112">
+      <c r="H9" s="98"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="97">
+        <v>25</v>
+      </c>
+      <c r="L9" s="98"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="97">
         <v>15</v>
       </c>
-      <c r="O9" s="113"/>
-      <c r="P9" s="113"/>
-      <c r="Q9" s="114"/>
+      <c r="O9" s="98"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="99"/>
     </row>
     <row r="10" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="96" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="84">
         <v>20</v>
@@ -3127,14 +3137,15 @@
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" customWidth="1"/>
     <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B1" s="90" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C1" s="90"/>
       <c r="D1" s="90"/>
@@ -3143,44 +3154,44 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="89" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="90" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C2" s="90" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D2" s="90" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E2" s="90"/>
       <c r="F2" s="90"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="89" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B3" s="90">
         <v>663366</v>
       </c>
       <c r="C3" s="90" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D3" s="90" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E3" s="90" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F3" s="90"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="89" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B4" s="90" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C4" s="90">
         <v>339966</v>
@@ -3195,22 +3206,22 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="89" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="90" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="90" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="90" t="s">
+      <c r="F5" s="90" t="s">
         <v>65</v>
-      </c>
-      <c r="C5" s="90" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="90" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="90" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="90" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Required weights.xlsx
+++ b/Required weights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofwaterloo-my.sharepoint.com/personal/maraji_uwaterloo_ca/Documents/Symbiosis Lab/Waqas/Side Projects/Bipartitie_3_way/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="553" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DA25437-D0C9-1E4B-AFA3-E89901CAC6D5}"/>
+  <xr:revisionPtr revIDLastSave="554" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C8B3788-BE81-A040-B594-5959A5A57997}"/>
   <bookViews>
-    <workbookView xWindow="-1940" yWindow="-18880" windowWidth="24080" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1940" yWindow="-19040" windowWidth="24080" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relationship Matrix" sheetId="7" r:id="rId1"/>
@@ -163,9 +163,6 @@
     <t>Verbal articulation</t>
   </si>
   <si>
-    <t>Graphic representation</t>
-  </si>
-  <si>
     <t>Maybe</t>
   </si>
   <si>
@@ -251,6 +248,9 @@
   </si>
   <si>
     <t>Criteria</t>
+  </si>
+  <si>
+    <t>Visual graphics</t>
   </si>
 </sst>
 </file>
@@ -1125,6 +1125,9 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1141,6 +1144,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1167,15 +1176,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1560,40 +1560,40 @@
   <sheetData>
     <row r="3" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="106"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="100" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="100" t="s">
+      <c r="B4" s="109"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="101" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="101"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="100" t="s">
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="101"/>
-      <c r="N4" s="102"/>
-      <c r="O4" s="100" t="s">
+      <c r="M4" s="102"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="103"/>
     </row>
     <row r="5" spans="2:27" ht="139.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="108"/>
-      <c r="C5" s="109"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="112"/>
       <c r="D5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="115" t="s">
-        <v>67</v>
+      <c r="E5" s="97" t="s">
+        <v>66</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>21</v>
@@ -1635,15 +1635,15 @@
         <v>23</v>
       </c>
       <c r="S5" s="79" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T5" s="88" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U5" s="88"/>
     </row>
     <row r="6" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="103" t="s">
+      <c r="B6" s="106" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -1694,7 +1694,7 @@
       <c r="R6" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="S6" s="113">
+      <c r="S6" s="104">
         <v>10</v>
       </c>
       <c r="T6">
@@ -1702,7 +1702,7 @@
       </c>
     </row>
     <row r="7" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="110"/>
+      <c r="B7" s="113"/>
       <c r="C7" s="23" t="s">
         <v>2</v>
       </c>
@@ -1751,13 +1751,13 @@
       <c r="R7" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="S7" s="113"/>
+      <c r="S7" s="104"/>
       <c r="T7">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="111"/>
+      <c r="B8" s="114"/>
       <c r="C8" s="35" t="s">
         <v>33</v>
       </c>
@@ -1806,7 +1806,7 @@
       <c r="R8" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="S8" s="113"/>
+      <c r="S8" s="104"/>
       <c r="T8">
         <v>50</v>
       </c>
@@ -1816,7 +1816,7 @@
       <c r="AA8" s="69"/>
     </row>
     <row r="9" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="106" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="15" t="s">
@@ -1867,7 +1867,7 @@
       <c r="R9" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="S9" s="113">
+      <c r="S9" s="104">
         <v>50</v>
       </c>
       <c r="T9">
@@ -1879,7 +1879,7 @@
       <c r="AA9" s="71"/>
     </row>
     <row r="10" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="110"/>
+      <c r="B10" s="113"/>
       <c r="C10" s="23" t="s">
         <v>34</v>
       </c>
@@ -1928,7 +1928,7 @@
       <c r="R10" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="S10" s="113"/>
+      <c r="S10" s="104"/>
       <c r="T10">
         <v>35</v>
       </c>
@@ -1938,7 +1938,7 @@
       <c r="AA10" s="73"/>
     </row>
     <row r="11" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="110"/>
+      <c r="B11" s="113"/>
       <c r="C11" s="23" t="s">
         <v>35</v>
       </c>
@@ -1987,7 +1987,7 @@
       <c r="R11" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="S11" s="113"/>
+      <c r="S11" s="104"/>
       <c r="T11">
         <v>40</v>
       </c>
@@ -1997,7 +1997,7 @@
       <c r="AA11" s="75"/>
     </row>
     <row r="12" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="111"/>
+      <c r="B12" s="114"/>
       <c r="C12" s="35" t="s">
         <v>36</v>
       </c>
@@ -2046,13 +2046,13 @@
       <c r="R12" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="S12" s="113"/>
+      <c r="S12" s="104"/>
       <c r="T12">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="103" t="s">
+      <c r="B13" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="15" t="s">
@@ -2103,7 +2103,7 @@
       <c r="R13" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="S13" s="113">
+      <c r="S13" s="104">
         <v>25</v>
       </c>
       <c r="T13">
@@ -2118,7 +2118,7 @@
       </c>
     </row>
     <row r="14" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="110"/>
+      <c r="B14" s="113"/>
       <c r="C14" s="23" t="s">
         <v>38</v>
       </c>
@@ -2167,7 +2167,7 @@
       <c r="R14" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="S14" s="113"/>
+      <c r="S14" s="104"/>
       <c r="T14">
         <v>40</v>
       </c>
@@ -2176,11 +2176,11 @@
       </c>
       <c r="Z14" s="62"/>
       <c r="AA14" s="65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="110"/>
+      <c r="B15" s="113"/>
       <c r="C15" s="23" t="s">
         <v>39</v>
       </c>
@@ -2229,20 +2229,20 @@
       <c r="R15" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="S15" s="113"/>
+      <c r="S15" s="104"/>
       <c r="T15">
         <v>25</v>
       </c>
       <c r="Y15" s="66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z15" s="62"/>
       <c r="AA15" s="67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="2:27" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="112"/>
+      <c r="B16" s="115"/>
       <c r="C16" s="48" t="s">
         <v>8</v>
       </c>
@@ -2291,13 +2291,13 @@
       <c r="R16" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="S16" s="113"/>
+      <c r="S16" s="104"/>
       <c r="T16">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="103" t="s">
+      <c r="B17" s="106" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="15" t="s">
@@ -2348,7 +2348,7 @@
       <c r="R17" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="S17" s="113">
+      <c r="S17" s="104">
         <v>15</v>
       </c>
       <c r="T17">
@@ -2356,9 +2356,9 @@
       </c>
     </row>
     <row r="18" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="104"/>
+      <c r="B18" s="107"/>
       <c r="C18" s="23" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D18" s="33" t="s">
         <v>25</v>
@@ -2405,13 +2405,13 @@
       <c r="R18" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="S18" s="113"/>
+      <c r="S18" s="104"/>
       <c r="T18">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="2:20" ht="17" x14ac:dyDescent="0.2">
-      <c r="B19" s="104"/>
+      <c r="B19" s="107"/>
       <c r="C19" s="57" t="s">
         <v>18</v>
       </c>
@@ -2460,13 +2460,13 @@
       <c r="R19" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="S19" s="113"/>
+      <c r="S19" s="104"/>
       <c r="T19">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="2:20" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="105"/>
+      <c r="B20" s="108"/>
       <c r="C20" s="58" t="s">
         <v>19</v>
       </c>
@@ -2515,49 +2515,41 @@
       <c r="R20" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="S20" s="113"/>
+      <c r="S20" s="104"/>
       <c r="T20">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C21" s="81" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="114">
+        <v>47</v>
+      </c>
+      <c r="D21" s="105">
         <v>40</v>
       </c>
-      <c r="E21" s="114"/>
-      <c r="F21" s="114"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="114">
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105">
         <v>30</v>
       </c>
-      <c r="I21" s="114"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="114"/>
-      <c r="L21" s="114">
+      <c r="I21" s="105"/>
+      <c r="J21" s="105"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="105">
         <v>20</v>
       </c>
-      <c r="M21" s="114"/>
-      <c r="N21" s="114"/>
-      <c r="O21" s="114">
+      <c r="M21" s="105"/>
+      <c r="N21" s="105"/>
+      <c r="O21" s="105">
         <v>10</v>
       </c>
-      <c r="P21" s="114"/>
-      <c r="Q21" s="114"/>
-      <c r="R21" s="114"/>
+      <c r="P21" s="105"/>
+      <c r="Q21" s="105"/>
+      <c r="R21" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="S9:S12"/>
-    <mergeCell ref="S13:S16"/>
-    <mergeCell ref="S17:S20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:R21"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="B4:C5"/>
     <mergeCell ref="O4:R4"/>
@@ -2567,6 +2559,14 @@
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="L4:N4"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="S9:S12"/>
+    <mergeCell ref="S13:S16"/>
+    <mergeCell ref="S17:S20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:R21"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:R20">
     <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="M">
@@ -2649,31 +2649,31 @@
     <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="82"/>
-      <c r="C2" s="100" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="100" t="s">
+      <c r="C2" s="101" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="100" t="s">
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="101"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="100" t="s">
+      <c r="L2" s="102"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="102"/>
+      <c r="O2" s="102"/>
+      <c r="P2" s="102"/>
+      <c r="Q2" s="103"/>
       <c r="R2" s="80" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="92" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>26</v>
@@ -2802,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="93" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>24</v>
@@ -2858,7 +2858,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>25</v>
@@ -3023,35 +3023,35 @@
     </row>
     <row r="9" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" s="95" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="97">
+        <v>47</v>
+      </c>
+      <c r="C9" s="98">
         <v>20</v>
       </c>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="97">
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="98">
         <v>40</v>
       </c>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="99"/>
-      <c r="K9" s="97">
-        <v>25</v>
-      </c>
-      <c r="L9" s="98"/>
-      <c r="M9" s="99"/>
-      <c r="N9" s="97">
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="98">
+        <v>25</v>
+      </c>
+      <c r="L9" s="99"/>
+      <c r="M9" s="100"/>
+      <c r="N9" s="98">
         <v>15</v>
       </c>
-      <c r="O9" s="98"/>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="100"/>
     </row>
     <row r="10" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="96" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="84">
         <v>20</v>
@@ -3142,10 +3142,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="90" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C1" s="90"/>
       <c r="D1" s="90"/>
@@ -3154,44 +3154,44 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="89" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="90" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" s="90" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2" s="90"/>
       <c r="F2" s="90"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="89" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="90">
         <v>663366</v>
       </c>
       <c r="C3" s="90" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="90" t="s">
+      <c r="E3" s="90" t="s">
         <v>56</v>
-      </c>
-      <c r="E3" s="90" t="s">
-        <v>57</v>
       </c>
       <c r="F3" s="90"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="89" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="90" t="s">
         <v>58</v>
-      </c>
-      <c r="B4" s="90" t="s">
-        <v>59</v>
       </c>
       <c r="C4" s="90">
         <v>339966</v>
@@ -3206,22 +3206,22 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="89" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="90" t="s">
+      <c r="C5" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="90" t="s">
+      <c r="D5" s="90" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="90" t="s">
+      <c r="E5" s="90" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="90" t="s">
+      <c r="F5" s="90" t="s">
         <v>64</v>
-      </c>
-      <c r="F5" s="90" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Required weights.xlsx
+++ b/Required weights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofwaterloo-my.sharepoint.com/personal/maraji_uwaterloo_ca/Documents/Symbiosis Lab/Waqas/Side Projects/Bipartitie_3_way/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="554" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C8B3788-BE81-A040-B594-5959A5A57997}"/>
+  <xr:revisionPtr revIDLastSave="810" documentId="13_ncr:1_{C4DF0E6E-FA3F-6D49-AAC4-27CBAFD82E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65C7CE55-5EDA-4748-BABA-19A692D6A587}"/>
   <bookViews>
-    <workbookView xWindow="-1940" yWindow="-19040" windowWidth="24080" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8160" yWindow="22740" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relationship Matrix" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="82">
   <si>
     <t>Communication</t>
   </si>
@@ -251,6 +251,39 @@
   </si>
   <si>
     <t>Visual graphics</t>
+  </si>
+  <si>
+    <t>connections score</t>
+  </si>
+  <si>
+    <t>0.25 * conn score</t>
+  </si>
+  <si>
+    <t>colW</t>
+  </si>
+  <si>
+    <t>CatW</t>
+  </si>
+  <si>
+    <t>0.75*(colW+CatW)</t>
+  </si>
+  <si>
+    <t>Impact score</t>
+  </si>
+  <si>
+    <t>medium conn (left to mid)</t>
+  </si>
+  <si>
+    <t>medium conn (mid to right)</t>
+  </si>
+  <si>
+    <t>strong Conn (left to mid)</t>
+  </si>
+  <si>
+    <t>strong Conn (mid to right)</t>
+  </si>
+  <si>
+    <t>RANK</t>
   </si>
 </sst>
 </file>
@@ -415,7 +448,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -454,8 +487,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="31">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -847,11 +892,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1128,13 +1213,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1144,43 +1241,101 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1541,13 +1696,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C516A866-194E-4597-9029-A5AD387CCDD1}">
-  <dimension ref="B3:AA21"/>
+  <dimension ref="B3:AA32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
     <col min="2" max="2" width="5" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" style="1" customWidth="1"/>
-    <col min="4" max="18" width="4.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1640625" style="1" customWidth="1"/>
+    <col min="5" max="8" width="4.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="4.1640625" style="1" customWidth="1"/>
     <col min="19" max="19" width="18.6640625" style="1" customWidth="1"/>
     <col min="23" max="24" width="8.83203125" style="1"/>
     <col min="25" max="25" width="4.1640625" style="1" customWidth="1"/>
@@ -1560,35 +1718,35 @@
   <sheetData>
     <row r="3" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="109"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="101" t="s">
+      <c r="B4" s="101"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="101" t="s">
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="103"/>
-      <c r="L4" s="101" t="s">
+      <c r="I4" s="106"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="102"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="101" t="s">
+      <c r="M4" s="106"/>
+      <c r="N4" s="107"/>
+      <c r="O4" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="102"/>
-      <c r="Q4" s="102"/>
-      <c r="R4" s="103"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="106"/>
+      <c r="R4" s="107"/>
     </row>
     <row r="5" spans="2:27" ht="139.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="111"/>
-      <c r="C5" s="112"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="104"/>
       <c r="D5" s="12" t="s">
         <v>7</v>
       </c>
@@ -1643,7 +1801,7 @@
       <c r="U5" s="88"/>
     </row>
     <row r="6" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="106" t="s">
+      <c r="B6" s="98" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -1694,7 +1852,7 @@
       <c r="R6" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="S6" s="104">
+      <c r="S6" s="111">
         <v>10</v>
       </c>
       <c r="T6">
@@ -1702,7 +1860,7 @@
       </c>
     </row>
     <row r="7" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="113"/>
+      <c r="B7" s="108"/>
       <c r="C7" s="23" t="s">
         <v>2</v>
       </c>
@@ -1751,13 +1909,13 @@
       <c r="R7" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="S7" s="104"/>
+      <c r="S7" s="111"/>
       <c r="T7">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="114"/>
+      <c r="B8" s="109"/>
       <c r="C8" s="35" t="s">
         <v>33</v>
       </c>
@@ -1806,7 +1964,7 @@
       <c r="R8" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="S8" s="104"/>
+      <c r="S8" s="111"/>
       <c r="T8">
         <v>50</v>
       </c>
@@ -1816,7 +1974,7 @@
       <c r="AA8" s="69"/>
     </row>
     <row r="9" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="106" t="s">
+      <c r="B9" s="98" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="15" t="s">
@@ -1867,7 +2025,7 @@
       <c r="R9" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="S9" s="104">
+      <c r="S9" s="111">
         <v>50</v>
       </c>
       <c r="T9">
@@ -1879,7 +2037,7 @@
       <c r="AA9" s="71"/>
     </row>
     <row r="10" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="113"/>
+      <c r="B10" s="108"/>
       <c r="C10" s="23" t="s">
         <v>34</v>
       </c>
@@ -1928,7 +2086,7 @@
       <c r="R10" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="S10" s="104"/>
+      <c r="S10" s="111"/>
       <c r="T10">
         <v>35</v>
       </c>
@@ -1938,7 +2096,7 @@
       <c r="AA10" s="73"/>
     </row>
     <row r="11" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="113"/>
+      <c r="B11" s="108"/>
       <c r="C11" s="23" t="s">
         <v>35</v>
       </c>
@@ -1987,7 +2145,7 @@
       <c r="R11" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="S11" s="104"/>
+      <c r="S11" s="111"/>
       <c r="T11">
         <v>40</v>
       </c>
@@ -1997,7 +2155,7 @@
       <c r="AA11" s="75"/>
     </row>
     <row r="12" spans="2:27" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="114"/>
+      <c r="B12" s="109"/>
       <c r="C12" s="35" t="s">
         <v>36</v>
       </c>
@@ -2046,13 +2204,13 @@
       <c r="R12" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="S12" s="104"/>
+      <c r="S12" s="111"/>
       <c r="T12">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="106" t="s">
+      <c r="B13" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="15" t="s">
@@ -2103,7 +2261,7 @@
       <c r="R13" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="S13" s="104">
+      <c r="S13" s="111">
         <v>25</v>
       </c>
       <c r="T13">
@@ -2118,7 +2276,7 @@
       </c>
     </row>
     <row r="14" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="113"/>
+      <c r="B14" s="108"/>
       <c r="C14" s="23" t="s">
         <v>38</v>
       </c>
@@ -2167,7 +2325,7 @@
       <c r="R14" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="S14" s="104"/>
+      <c r="S14" s="111"/>
       <c r="T14">
         <v>40</v>
       </c>
@@ -2180,7 +2338,7 @@
       </c>
     </row>
     <row r="15" spans="2:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="113"/>
+      <c r="B15" s="108"/>
       <c r="C15" s="23" t="s">
         <v>39</v>
       </c>
@@ -2229,7 +2387,7 @@
       <c r="R15" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="S15" s="104"/>
+      <c r="S15" s="111"/>
       <c r="T15">
         <v>25</v>
       </c>
@@ -2242,7 +2400,7 @@
       </c>
     </row>
     <row r="16" spans="2:27" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="115"/>
+      <c r="B16" s="110"/>
       <c r="C16" s="48" t="s">
         <v>8</v>
       </c>
@@ -2291,13 +2449,13 @@
       <c r="R16" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="S16" s="104"/>
+      <c r="S16" s="111"/>
       <c r="T16">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="106" t="s">
+      <c r="B17" s="98" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="15" t="s">
@@ -2348,7 +2506,7 @@
       <c r="R17" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="S17" s="104">
+      <c r="S17" s="111">
         <v>15</v>
       </c>
       <c r="T17">
@@ -2356,7 +2514,7 @@
       </c>
     </row>
     <row r="18" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="107"/>
+      <c r="B18" s="99"/>
       <c r="C18" s="23" t="s">
         <v>70</v>
       </c>
@@ -2405,13 +2563,13 @@
       <c r="R18" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="S18" s="104"/>
+      <c r="S18" s="111"/>
       <c r="T18">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="2:20" ht="17" x14ac:dyDescent="0.2">
-      <c r="B19" s="107"/>
+      <c r="B19" s="99"/>
       <c r="C19" s="57" t="s">
         <v>18</v>
       </c>
@@ -2460,13 +2618,13 @@
       <c r="R19" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="S19" s="104"/>
+      <c r="S19" s="111"/>
       <c r="T19">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="2:20" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="108"/>
+      <c r="B20" s="100"/>
       <c r="C20" s="58" t="s">
         <v>19</v>
       </c>
@@ -2515,7 +2673,7 @@
       <c r="R20" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="S20" s="104"/>
+      <c r="S20" s="111"/>
       <c r="T20">
         <v>10</v>
       </c>
@@ -2524,32 +2682,759 @@
       <c r="C21" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="105">
+      <c r="D21" s="112">
+        <f>mid2right!C9</f>
+        <v>20</v>
+      </c>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="132">
+        <f>mid2right!G9</f>
         <v>40</v>
       </c>
-      <c r="E21" s="105"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105">
+      <c r="I21" s="133"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="134"/>
+      <c r="L21" s="112">
+        <f>mid2right!K9</f>
+        <v>25</v>
+      </c>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="132">
+        <f>mid2right!N9</f>
+        <v>15</v>
+      </c>
+      <c r="P21" s="133"/>
+      <c r="Q21" s="133"/>
+      <c r="R21" s="134"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="116">
+        <f t="shared" ref="D22:H22" si="0">COUNTIF(D6:D20,"S")</f>
+        <v>1</v>
+      </c>
+      <c r="E22" s="116">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="F22" s="116">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G22" s="116">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H22" s="120">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I22" s="121">
+        <f>COUNTIF(I6:I20,"S")</f>
+        <v>10</v>
+      </c>
+      <c r="J22" s="121">
+        <f t="shared" ref="J22:R22" si="1">COUNTIF(J6:J20,"S")</f>
+        <v>2</v>
+      </c>
+      <c r="K22" s="122">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L22" s="116">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="M22" s="116">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="N22" s="116">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="O22" s="120">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="P22" s="121">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q22" s="121">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="R22" s="122">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="116">
+        <f>COUNTIF(mid2right!C4:C8, "S")*1</f>
+        <v>1</v>
+      </c>
+      <c r="E23" s="116">
+        <f>COUNTIF(mid2right!D4:D8, "S")*1</f>
+        <v>3</v>
+      </c>
+      <c r="F23" s="116">
+        <f>COUNTIF(mid2right!E4:E8, "S")*1</f>
+        <v>1</v>
+      </c>
+      <c r="G23" s="116">
+        <f>COUNTIF(mid2right!F4:F8, "S")*1</f>
+        <v>2</v>
+      </c>
+      <c r="H23" s="120">
+        <f>COUNTIF(mid2right!G4:G8, "S")*1</f>
+        <v>4</v>
+      </c>
+      <c r="I23" s="121">
+        <f>COUNTIF(mid2right!H4:H8, "S")*1</f>
+        <v>4</v>
+      </c>
+      <c r="J23" s="121">
+        <f>COUNTIF(mid2right!I4:I8, "S")*1</f>
+        <v>2</v>
+      </c>
+      <c r="K23" s="122">
+        <f>COUNTIF(mid2right!J4:J8, "S")*1</f>
+        <v>2</v>
+      </c>
+      <c r="L23" s="116">
+        <f>COUNTIF(mid2right!K4:K8, "S")*1</f>
+        <v>1</v>
+      </c>
+      <c r="M23" s="116">
+        <f>COUNTIF(mid2right!L4:L8, "S")*1</f>
+        <v>1</v>
+      </c>
+      <c r="N23" s="116">
+        <f>COUNTIF(mid2right!M4:M8, "S")*1</f>
+        <v>2</v>
+      </c>
+      <c r="O23" s="120">
+        <f>COUNTIF(mid2right!N4:N8, "S")*1</f>
+        <v>3</v>
+      </c>
+      <c r="P23" s="121">
+        <f>COUNTIF(mid2right!O4:O8, "S")*1</f>
+        <v>3</v>
+      </c>
+      <c r="Q23" s="121">
+        <f>COUNTIF(mid2right!P4:P8, "S")*1</f>
+        <v>1</v>
+      </c>
+      <c r="R23" s="122">
+        <f>COUNTIF(mid2right!Q4:Q8, "S")*1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="117">
+        <f>COUNTIF(D6:D20,"M")</f>
+        <v>3</v>
+      </c>
+      <c r="E24" s="117">
+        <f t="shared" ref="E24:R24" si="2">COUNTIF(E6:E20,"M")</f>
+        <v>3</v>
+      </c>
+      <c r="F24" s="117">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="G24" s="117">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H24" s="123">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I24" s="124">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J24" s="124">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="K24" s="125">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L24" s="117">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="117">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="N24" s="117">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="O24" s="123">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="P24" s="124">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="Q24" s="124">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="R24" s="125">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="117">
+        <f>COUNTIF(mid2right!C4:C8,"M")</f>
+        <v>1</v>
+      </c>
+      <c r="E25" s="117">
+        <f>COUNTIF(mid2right!D4:D8,"M")</f>
+        <v>2</v>
+      </c>
+      <c r="F25" s="117">
+        <f>COUNTIF(mid2right!E4:E8,"M")</f>
+        <v>4</v>
+      </c>
+      <c r="G25" s="117">
+        <f>COUNTIF(mid2right!F4:F8,"M")</f>
+        <v>1</v>
+      </c>
+      <c r="H25" s="123">
+        <f>COUNTIF(mid2right!G4:G8,"M")</f>
+        <v>1</v>
+      </c>
+      <c r="I25" s="124">
+        <f>COUNTIF(mid2right!H4:H8,"M")</f>
+        <v>1</v>
+      </c>
+      <c r="J25" s="124">
+        <f>COUNTIF(mid2right!I4:I8,"M")</f>
+        <v>3</v>
+      </c>
+      <c r="K25" s="125">
+        <f>COUNTIF(mid2right!J4:J8,"M")</f>
+        <v>2</v>
+      </c>
+      <c r="L25" s="117">
+        <f>COUNTIF(mid2right!K4:K8,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="117">
+        <f>COUNTIF(mid2right!L4:L8,"M")</f>
+        <v>4</v>
+      </c>
+      <c r="N25" s="117">
+        <f>COUNTIF(mid2right!M4:M8,"M")</f>
+        <v>2</v>
+      </c>
+      <c r="O25" s="123">
+        <f>COUNTIF(mid2right!N4:N8,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="124">
+        <f>COUNTIF(mid2right!O4:O8,"M")</f>
+        <v>2</v>
+      </c>
+      <c r="Q25" s="124">
+        <f>COUNTIF(mid2right!P4:P8,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="125">
+        <f>COUNTIF(mid2right!Q4:Q8,"M")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" ref="D26:H26" si="3">3*SUM(D22:D23) + SUM(D24:D25)</f>
+        <v>10</v>
+      </c>
+      <c r="E26" s="1">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="G26" s="1">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="H26" s="126">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="I26" s="127">
+        <f>3*SUM(I22:I23) + SUM(I24:I25)</f>
+        <v>45</v>
+      </c>
+      <c r="J26" s="127">
+        <f t="shared" ref="J26:R26" si="4">3*SUM(J22:J23) + SUM(J24:J25)</f>
+        <v>22</v>
+      </c>
+      <c r="K26" s="128">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="L26" s="1">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="M26" s="1">
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="105"/>
-      <c r="L21" s="105">
+      <c r="N26" s="1">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+      <c r="O26" s="126">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+      <c r="P26" s="127">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="Q26" s="127">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="R26" s="128">
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="M21" s="105"/>
-      <c r="N21" s="105"/>
-      <c r="O21" s="105">
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" ref="D27:H27" si="5">0.25*D26</f>
+        <v>2.5</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="5"/>
+        <v>9.5</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="5"/>
+        <v>5.75</v>
+      </c>
+      <c r="H27" s="126">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="I27" s="127">
+        <f>0.25*I26</f>
+        <v>11.25</v>
+      </c>
+      <c r="J27" s="127">
+        <f t="shared" ref="J27:R27" si="6">0.25*J26</f>
+        <v>5.5</v>
+      </c>
+      <c r="K27" s="128">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="L27" s="1">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="M27" s="1">
+        <f t="shared" si="6"/>
+        <v>7.5</v>
+      </c>
+      <c r="N27" s="1">
+        <f t="shared" si="6"/>
+        <v>8.25</v>
+      </c>
+      <c r="O27" s="126">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="P27" s="127">
+        <f t="shared" si="6"/>
+        <v>5.25</v>
+      </c>
+      <c r="Q27" s="127">
+        <f t="shared" si="6"/>
+        <v>3.25</v>
+      </c>
+      <c r="R27" s="128">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C28" s="118" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="118">
+        <f>mid2right!C10*mid2right!C9/100</f>
+        <v>4</v>
+      </c>
+      <c r="E28" s="118">
+        <f>mid2right!D10*mid2right!C9/100</f>
+        <v>6</v>
+      </c>
+      <c r="F28" s="118">
+        <f>mid2right!E10*mid2right!C9/100</f>
+        <v>3</v>
+      </c>
+      <c r="G28" s="118">
+        <f>mid2right!F10*mid2right!C9/100</f>
+        <v>7</v>
+      </c>
+      <c r="H28" s="129">
+        <f>mid2right!G10*mid2right!G9/100</f>
         <v>10</v>
       </c>
-      <c r="P21" s="105"/>
-      <c r="Q21" s="105"/>
-      <c r="R21" s="105"/>
+      <c r="I28" s="130">
+        <f>mid2right!H10*mid2right!G9/100</f>
+        <v>12</v>
+      </c>
+      <c r="J28" s="130">
+        <f>mid2right!I10*mid2right!G9/100</f>
+        <v>12</v>
+      </c>
+      <c r="K28" s="131">
+        <f>mid2right!J10*mid2right!G9/100</f>
+        <v>6</v>
+      </c>
+      <c r="L28" s="118">
+        <f>mid2right!K10*mid2right!K9/100</f>
+        <v>7.5</v>
+      </c>
+      <c r="M28" s="118">
+        <f>mid2right!L10*mid2right!K9/100</f>
+        <v>7.5</v>
+      </c>
+      <c r="N28" s="118">
+        <f>mid2right!M10*mid2right!K9/100</f>
+        <v>10</v>
+      </c>
+      <c r="O28" s="129">
+        <f>mid2right!N10*mid2right!N9/100</f>
+        <v>5.25</v>
+      </c>
+      <c r="P28" s="130">
+        <f>mid2right!O10*mid2right!N9/100</f>
+        <v>3.75</v>
+      </c>
+      <c r="Q28" s="130">
+        <f>mid2right!P10*mid2right!N9/100</f>
+        <v>3.75</v>
+      </c>
+      <c r="R28" s="131">
+        <f>mid2right!Q10*mid2right!N9/100</f>
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="118" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="118">
+        <f>mid2right!C10</f>
+        <v>20</v>
+      </c>
+      <c r="E29" s="118">
+        <f>mid2right!D10</f>
+        <v>30</v>
+      </c>
+      <c r="F29" s="118">
+        <f>mid2right!E10</f>
+        <v>15</v>
+      </c>
+      <c r="G29" s="118">
+        <f>mid2right!F10</f>
+        <v>35</v>
+      </c>
+      <c r="H29" s="135">
+        <f>mid2right!G10</f>
+        <v>25</v>
+      </c>
+      <c r="I29" s="136">
+        <f>mid2right!H10</f>
+        <v>30</v>
+      </c>
+      <c r="J29" s="136">
+        <f>mid2right!I10</f>
+        <v>30</v>
+      </c>
+      <c r="K29" s="137">
+        <f>mid2right!J10</f>
+        <v>15</v>
+      </c>
+      <c r="L29" s="118">
+        <f>mid2right!K10</f>
+        <v>30</v>
+      </c>
+      <c r="M29" s="118">
+        <f>mid2right!L10</f>
+        <v>30</v>
+      </c>
+      <c r="N29" s="118">
+        <f>mid2right!M10</f>
+        <v>40</v>
+      </c>
+      <c r="O29" s="135">
+        <f>mid2right!N10</f>
+        <v>35</v>
+      </c>
+      <c r="P29" s="136">
+        <f>mid2right!O10</f>
+        <v>25</v>
+      </c>
+      <c r="Q29" s="136">
+        <f>mid2right!P10</f>
+        <v>25</v>
+      </c>
+      <c r="R29" s="137">
+        <f>mid2right!Q10</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="1">
+        <f>0.75*D28*D29</f>
+        <v>60</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" ref="E30:R30" si="7">0.75*E28*E29</f>
+        <v>135</v>
+      </c>
+      <c r="F30" s="1">
+        <f t="shared" si="7"/>
+        <v>33.75</v>
+      </c>
+      <c r="G30" s="1">
+        <f t="shared" si="7"/>
+        <v>183.75</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="7"/>
+        <v>187.5</v>
+      </c>
+      <c r="I30" s="1">
+        <f t="shared" si="7"/>
+        <v>270</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="7"/>
+        <v>270</v>
+      </c>
+      <c r="K30" s="1">
+        <f t="shared" si="7"/>
+        <v>67.5</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" si="7"/>
+        <v>168.75</v>
+      </c>
+      <c r="M30" s="1">
+        <f t="shared" si="7"/>
+        <v>168.75</v>
+      </c>
+      <c r="N30" s="1">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="O30" s="1">
+        <f t="shared" si="7"/>
+        <v>137.8125</v>
+      </c>
+      <c r="P30" s="1">
+        <f t="shared" si="7"/>
+        <v>70.3125</v>
+      </c>
+      <c r="Q30" s="1">
+        <f t="shared" si="7"/>
+        <v>70.3125</v>
+      </c>
+      <c r="R30" s="1">
+        <f t="shared" si="7"/>
+        <v>25.3125</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="1">
+        <f t="shared" ref="D31:H31" si="8">D30+D27</f>
+        <v>62.5</v>
+      </c>
+      <c r="E31" s="1">
+        <f t="shared" si="8"/>
+        <v>144.5</v>
+      </c>
+      <c r="F31" s="1">
+        <f t="shared" si="8"/>
+        <v>38.75</v>
+      </c>
+      <c r="G31" s="1">
+        <f t="shared" si="8"/>
+        <v>189.5</v>
+      </c>
+      <c r="H31" s="1">
+        <f t="shared" si="8"/>
+        <v>198.5</v>
+      </c>
+      <c r="I31" s="1">
+        <f>I30+I27</f>
+        <v>281.25</v>
+      </c>
+      <c r="J31" s="1">
+        <f t="shared" ref="J31:R31" si="9">J30+J27</f>
+        <v>275.5</v>
+      </c>
+      <c r="K31" s="1">
+        <f t="shared" si="9"/>
+        <v>73.5</v>
+      </c>
+      <c r="L31" s="1">
+        <f t="shared" si="9"/>
+        <v>174.75</v>
+      </c>
+      <c r="M31" s="1">
+        <f t="shared" si="9"/>
+        <v>176.25</v>
+      </c>
+      <c r="N31" s="1">
+        <f t="shared" si="9"/>
+        <v>308.25</v>
+      </c>
+      <c r="O31" s="1">
+        <f t="shared" si="9"/>
+        <v>145.8125</v>
+      </c>
+      <c r="P31" s="1">
+        <f t="shared" si="9"/>
+        <v>75.5625</v>
+      </c>
+      <c r="Q31" s="1">
+        <f t="shared" si="9"/>
+        <v>73.5625</v>
+      </c>
+      <c r="R31" s="1">
+        <f t="shared" si="9"/>
+        <v>30.3125</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="C32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="1">
+        <f>_xlfn.RANK.EQ(D31,$D$31:$R$31)</f>
+        <v>13</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" ref="E32:R32" si="10">_xlfn.RANK.EQ(E31,$D$31:$R$31)</f>
+        <v>9</v>
+      </c>
+      <c r="F32" s="1">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="G32" s="1">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="H32" s="1">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="I32" s="1">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="J32" s="1">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="K32" s="1">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="L32" s="1">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="M32" s="1">
+        <f t="shared" si="10"/>
+        <v>6</v>
+      </c>
+      <c r="N32" s="1">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O32" s="1">
+        <f t="shared" si="10"/>
+        <v>8</v>
+      </c>
+      <c r="P32" s="1">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="Q32" s="1">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="R32" s="1">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="S9:S12"/>
+    <mergeCell ref="S13:S16"/>
+    <mergeCell ref="S17:S20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:R21"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="B4:C5"/>
     <mergeCell ref="O4:R4"/>
@@ -2559,27 +3444,31 @@
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="L4:N4"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="S9:S12"/>
-    <mergeCell ref="S13:S16"/>
-    <mergeCell ref="S17:S20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:R21"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:R20">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="W">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="W">
       <formula>NOT(ISERROR(SEARCH("W",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="S">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="S">
       <formula>NOT(ISERROR(SEARCH("S",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="N">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="N">
       <formula>NOT(ISERROR(SEARCH("N",D6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D31:R31">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2589,12 +3478,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC40F516-73D9-AF40-BBFA-DA5A09FC7B78}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1640625" customWidth="1"/>
-    <col min="3" max="17" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.83203125" customWidth="1"/>
+    <col min="4" max="17" width="3.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2649,29 +3539,29 @@
     <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="82"/>
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="101" t="s">
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="101" t="s">
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="102"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="101" t="s">
+      <c r="L2" s="106"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="102"/>
-      <c r="P2" s="102"/>
-      <c r="Q2" s="103"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="107"/>
       <c r="R2" s="80" t="s">
         <v>47</v>
       </c>
@@ -3025,29 +3915,29 @@
       <c r="B9" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="98">
+      <c r="C9" s="113">
         <v>20</v>
       </c>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="98">
+      <c r="D9" s="114"/>
+      <c r="E9" s="114"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="113">
         <v>40</v>
       </c>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="100"/>
-      <c r="K9" s="98">
-        <v>25</v>
-      </c>
-      <c r="L9" s="99"/>
-      <c r="M9" s="100"/>
-      <c r="N9" s="98">
+      <c r="H9" s="114"/>
+      <c r="I9" s="114"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="113">
+        <v>25</v>
+      </c>
+      <c r="L9" s="114"/>
+      <c r="M9" s="115"/>
+      <c r="N9" s="113">
         <v>15</v>
       </c>
-      <c r="O9" s="99"/>
-      <c r="P9" s="99"/>
-      <c r="Q9" s="100"/>
+      <c r="O9" s="114"/>
+      <c r="P9" s="114"/>
+      <c r="Q9" s="115"/>
     </row>
     <row r="10" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="96" t="s">
@@ -3078,13 +3968,13 @@
         <v>15</v>
       </c>
       <c r="K10" s="84">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L10" s="85">
         <v>30</v>
       </c>
       <c r="M10" s="86">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N10" s="84">
         <v>35</v>
@@ -3098,6 +3988,9 @@
       <c r="Q10" s="86">
         <v>15</v>
       </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C11" s="119"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3111,16 +4004,16 @@
     <mergeCell ref="K2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:Q8">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",C4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="W">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="W">
       <formula>NOT(ISERROR(SEARCH("W",C4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="S">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="S">
       <formula>NOT(ISERROR(SEARCH("S",C4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="N">
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="N">
       <formula>NOT(ISERROR(SEARCH("N",C4)))</formula>
     </cfRule>
   </conditionalFormatting>
